--- a/data/bist_screener_2026-04-02.xlsx
+++ b/data/bist_screener_2026-04-02.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Net gelir artışıTTM YY</t>
+          <t>Net gelir artışıÇeyreklik QQ</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -567,7 +567,7 @@
         <v>-0.2178</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-2.8787</v>
+        <v>-2.871</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         <v>0.1942</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>2.9681</v>
+        <v>-1.5643</v>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>0.0252</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4.823399999999999</v>
+        <v>-0.4697</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -700,9 +700,7 @@
       <c r="H5" s="6" t="n">
         <v>0.1498</v>
       </c>
-      <c r="I5" s="6" t="n">
-        <v>0.0071</v>
-      </c>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -747,7 +745,7 @@
         <v>0.0251</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3505</v>
+        <v>-0.8592</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -791,7 +789,7 @@
         <v>-0.2389</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-3.8158</v>
+        <v>-3.2783</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
@@ -835,7 +833,7 @@
         <v>-0.008800000000000001</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-1.4893</v>
+        <v>0.6854</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -880,8 +878,10 @@
       <c r="H9" s="6" t="n">
         <v>0.0115</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <v>-0.8969</v>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>-1.306.14</t>
+        </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
@@ -926,9 +926,7 @@
       <c r="H10" s="3" t="n">
         <v>0.0694</v>
       </c>
-      <c r="I10" s="3" t="n">
-        <v>0.8187000000000001</v>
-      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -971,7 +969,7 @@
         <v>-0.0037</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-1.1368</v>
+        <v>-2.3084</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -1014,11 +1012,7 @@
       <c r="H12" s="3" t="n">
         <v>-0.0291</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-2.596.25</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -1062,7 +1056,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>-4.017.29</t>
+          <t>-1.131.75</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1109,7 +1103,7 @@
         <v>0.0551</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.2263</v>
+        <v>0.1614</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1199,7 +1193,7 @@
         <v>0.0192</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.8983</v>
+        <v>-3.7063</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1238,8 +1232,10 @@
       <c r="H17" s="6" t="n">
         <v>-0.2471</v>
       </c>
-      <c r="I17" s="6" t="n">
-        <v>-0.07780000000000001</v>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>-1.680.98</t>
+        </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
@@ -1283,7 +1279,7 @@
         <v>-0.09269999999999999</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4338</v>
+        <v>-0.87</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1328,9 +1324,7 @@
       <c r="H19" s="6" t="n">
         <v>0.1073</v>
       </c>
-      <c r="I19" s="6" t="n">
-        <v>-0.3385</v>
-      </c>
+      <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -1373,7 +1367,7 @@
         <v>-0.059</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.4536</v>
+        <v>-0.2039</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1413,7 @@
         <v>0.0892</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.8844</v>
+        <v>2.9159</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
@@ -1462,9 +1456,7 @@
       <c r="H22" s="3" t="n">
         <v>-0.0512</v>
       </c>
-      <c r="I22" s="3" t="n">
-        <v>0.1897</v>
-      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -1505,7 +1497,7 @@
         <v>0.0219</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.4742</v>
+        <v>9.1807</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
@@ -1549,7 +1541,7 @@
         <v>-0.06480000000000001</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2994</v>
+        <v>-1.0115</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -1594,8 +1586,10 @@
       <c r="H25" s="6" t="n">
         <v>0.3101</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <v>9.867799999999999</v>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>+2.842.63</t>
+        </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
@@ -1640,7 +1634,11 @@
       <c r="H26" s="3" t="n">
         <v>0.3256</v>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>+337.694.54</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -1724,10 +1722,8 @@
       <c r="H28" s="3" t="n">
         <v>0.0208</v>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>+1.451.12</t>
-        </is>
+      <c r="I28" s="3" t="n">
+        <v>-1.7377</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1767,7 @@
         <v>-0.7939000000000001</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-1.609</v>
+        <v>-1.4176</v>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
@@ -1814,7 +1810,9 @@
       <c r="H30" s="3" t="n">
         <v>-0.0007000000000000001</v>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="3" t="n">
+        <v>0.07440000000000001</v>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -1859,7 +1857,7 @@
         <v>0.114</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.3328</v>
+        <v>-0.6793</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
@@ -1904,8 +1902,10 @@
       <c r="H32" s="3" t="n">
         <v>0.0341</v>
       </c>
-      <c r="I32" s="3" t="n">
-        <v>-0.7472</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>+1.355.23</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>0.0178</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.5034000000000001</v>
+        <v>6.4634</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>-0.095</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.008100000000000001</v>
+        <v>-5.725</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>-0.04269999999999999</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.4802</v>
+        <v>0.8924</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
@@ -2084,11 +2084,7 @@
       <c r="H36" s="3" t="n">
         <v>0.0118</v>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>+48.563.84</t>
-        </is>
-      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -2131,7 +2127,7 @@
         <v>-0.0209</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-2.3676</v>
+        <v>-0.08259999999999999</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
@@ -2175,7 +2171,7 @@
         <v>-0.0231</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.4384</v>
+        <v>-0.0625</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -2221,7 +2217,7 @@
         <v>0.1441</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3.0657</v>
+        <v>-0.5678</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
@@ -2264,7 +2260,9 @@
       <c r="H40" s="3" t="n">
         <v>-0.1298</v>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="3" t="n">
+        <v>0.4484</v>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -2308,7 +2306,11 @@
       <c r="H41" s="6" t="n">
         <v>0.4348</v>
       </c>
-      <c r="I41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>+2.741.43</t>
+        </is>
+      </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -2349,7 +2351,7 @@
         <v>0.1041</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>-0.5482</v>
+        <v>-0.7025</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -2393,7 +2395,7 @@
         <v>-0.0231</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.4384</v>
+        <v>-0.0625</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
@@ -2436,9 +2438,7 @@
       <c r="H44" s="3" t="n">
         <v>-0.0236</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>0.7669</v>
-      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -2481,7 +2481,7 @@
         <v>-0.06950000000000001</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-4.5107</v>
+        <v>-3.2954</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>-0.0462</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-1.8505</v>
+        <v>-4.5264</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>-0.059</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.2507</v>
+        <v>-2.8382</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>0.1486</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.0426</v>
+        <v>-0.3373</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>-1.496.08</t>
+          <t>-6.357.42</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -2705,7 +2705,7 @@
         <v>-0.1024</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>-2.6974</v>
+        <v>-0.4838</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -2748,8 +2748,10 @@
       <c r="H51" s="6" t="n">
         <v>-0.1015</v>
       </c>
-      <c r="I51" s="6" t="n">
-        <v>-4.835199999999999</v>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>-35.643.49</t>
+        </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
@@ -2795,7 +2797,7 @@
         <v>0.2726</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>5.0818</v>
+        <v>4.7406</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -2841,7 +2843,7 @@
         <v>0.0825</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.1842</v>
+        <v>3.5434</v>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
@@ -2885,7 +2887,7 @@
         <v>-0.2148</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>-0.3654</v>
+        <v>-1.5579</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -2930,7 +2932,9 @@
       <c r="H55" s="6" t="n">
         <v>0.0106</v>
       </c>
-      <c r="I55" s="5" t="inlineStr"/>
+      <c r="I55" s="6" t="n">
+        <v>-1.6389</v>
+      </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -2974,7 +2978,9 @@
       <c r="H56" s="3" t="n">
         <v>0.0567</v>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="3" t="n">
+        <v>-1.1035</v>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -3019,7 +3025,7 @@
         <v>0.0401</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.5951</v>
+        <v>5.243200000000001</v>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
@@ -3062,9 +3068,7 @@
       <c r="H58" s="3" t="n">
         <v>-0.06150000000000001</v>
       </c>
-      <c r="I58" s="3" t="n">
-        <v>-0.3827</v>
-      </c>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -3108,8 +3112,10 @@
       <c r="H59" s="6" t="n">
         <v>0.0692</v>
       </c>
-      <c r="I59" s="6" t="n">
-        <v>4.992900000000001</v>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>+1.423.82</t>
+        </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
@@ -3198,7 +3204,7 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>-2.467.88</t>
+          <t>-11.450.83</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
@@ -3243,7 +3249,7 @@
         <v>-0.0125</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>-1.4264</v>
+        <v>-1.2814</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3294,9 @@
       <c r="H63" s="6" t="n">
         <v>0.0128</v>
       </c>
-      <c r="I63" s="5" t="inlineStr"/>
+      <c r="I63" s="6" t="n">
+        <v>5.750299999999999</v>
+      </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -3330,8 +3338,10 @@
       <c r="H64" s="3" t="n">
         <v>-0.1339</v>
       </c>
-      <c r="I64" s="3" t="n">
-        <v>-0.7705</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-1.978.54</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -3375,7 +3385,7 @@
         <v>-0.0585</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>-1.2453</v>
+        <v>-1.1066</v>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
@@ -3418,8 +3428,10 @@
       <c r="H66" s="3" t="n">
         <v>-0.4023</v>
       </c>
-      <c r="I66" s="3" t="n">
-        <v>-0.5828</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-1.364.20</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -3465,7 +3477,7 @@
         <v>0.0371</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>-0.6311</v>
+        <v>2.5571</v>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
@@ -3509,7 +3521,7 @@
         <v>-0.0537</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>-2.698</v>
+        <v>-4.4859</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -3555,7 +3567,7 @@
         <v>0.0582</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>-0.3918</v>
+        <v>2.9142</v>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
@@ -3598,9 +3610,7 @@
       <c r="H70" s="3" t="n">
         <v>-0.07629999999999999</v>
       </c>
-      <c r="I70" s="3" t="n">
-        <v>-5.557300000000001</v>
-      </c>
+      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -3642,8 +3652,10 @@
       <c r="H71" s="6" t="n">
         <v>-0.1087</v>
       </c>
-      <c r="I71" s="6" t="n">
-        <v>0.0385</v>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>-3.137.90</t>
+        </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
@@ -3686,9 +3698,7 @@
       <c r="H72" s="3" t="n">
         <v>-0.1067</v>
       </c>
-      <c r="I72" s="3" t="n">
-        <v>-0.5694</v>
-      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -3732,8 +3742,10 @@
       <c r="H73" s="6" t="n">
         <v>0.0452</v>
       </c>
-      <c r="I73" s="6" t="n">
-        <v>-0.6107</v>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>-2.331.57</t>
+        </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
@@ -3779,7 +3791,7 @@
         <v>0.0443</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.1673</v>
+        <v>1.8264</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -3824,7 +3836,9 @@
       <c r="H75" s="6" t="n">
         <v>0.0386</v>
       </c>
-      <c r="I75" s="5" t="inlineStr"/>
+      <c r="I75" s="6" t="n">
+        <v>0.095</v>
+      </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -3868,9 +3882,7 @@
       <c r="H76" s="3" t="n">
         <v>0.013</v>
       </c>
-      <c r="I76" s="3" t="n">
-        <v>-0.2607</v>
-      </c>
+      <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Dağıtım servisleri</t>
@@ -3913,7 +3925,7 @@
         <v>-0.1555</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>-6.891900000000001</v>
+        <v>-1.5785</v>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
@@ -3958,8 +3970,10 @@
       <c r="H78" s="3" t="n">
         <v>0.0253</v>
       </c>
-      <c r="I78" s="3" t="n">
-        <v>-0.5434</v>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>+1.611.68</t>
+        </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -4003,7 +4017,7 @@
         <v>-0.2002</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>-2.3609</v>
+        <v>-7.1936</v>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
@@ -4047,7 +4061,7 @@
         <v>-0.0541</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-4.3773</v>
+        <v>-9.4055</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -4092,7 +4106,9 @@
       <c r="H81" s="6" t="n">
         <v>0.2986</v>
       </c>
-      <c r="I81" s="5" t="inlineStr"/>
+      <c r="I81" s="6" t="n">
+        <v>-1.5684</v>
+      </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -4136,9 +4152,7 @@
       <c r="H82" s="3" t="n">
         <v>0.0143</v>
       </c>
-      <c r="I82" s="3" t="n">
-        <v>-0.6718000000000001</v>
-      </c>
+      <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -4180,9 +4194,7 @@
       <c r="H83" s="6" t="n">
         <v>-0.0034</v>
       </c>
-      <c r="I83" s="6" t="n">
-        <v>-1.0646</v>
-      </c>
+      <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr">
         <is>
           <t>Enerji-dışı mineraller</t>
@@ -4221,7 +4233,7 @@
         <v>-0.047</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>-1.6447</v>
+        <v>0.1821</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -4266,7 +4278,9 @@
       <c r="H85" s="6" t="n">
         <v>0.1722</v>
       </c>
-      <c r="I85" s="5" t="inlineStr"/>
+      <c r="I85" s="6" t="n">
+        <v>9.006599999999999</v>
+      </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -4353,7 +4367,7 @@
         <v>-0.0335</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>0.711</v>
+        <v>-1.222</v>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
@@ -4399,7 +4413,7 @@
         <v>0.0246</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.485</v>
+        <v>-1.5979</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -4444,9 +4458,7 @@
       <c r="H89" s="6" t="n">
         <v>0.004500000000000001</v>
       </c>
-      <c r="I89" s="6" t="n">
-        <v>-0.915</v>
-      </c>
+      <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="5" t="inlineStr">
         <is>
           <t>Çeşitli Hizmetler</t>
@@ -4488,8 +4500,10 @@
       <c r="H90" s="3" t="n">
         <v>-0.0568</v>
       </c>
-      <c r="I90" s="3" t="n">
-        <v>-1.9626</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-2.434.09</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -4535,7 +4549,7 @@
         <v>0.0265</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>-0.6759999999999999</v>
+        <v>-0.2732</v>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
@@ -4579,7 +4593,7 @@
         <v>-0.1402</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>-1.005</v>
+        <v>-1.5387</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -4624,7 +4638,9 @@
       <c r="H93" s="6" t="n">
         <v>0.3644</v>
       </c>
-      <c r="I93" s="5" t="inlineStr"/>
+      <c r="I93" s="6" t="n">
+        <v>7.844600000000001</v>
+      </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
           <t>Sağlık teknolojisi</t>
@@ -4667,7 +4683,7 @@
         <v>-0.0946</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>-2.3646</v>
+        <v>-1.7395</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -4712,7 +4728,9 @@
       <c r="H95" s="6" t="n">
         <v>0.0237</v>
       </c>
-      <c r="I95" s="5" t="inlineStr"/>
+      <c r="I95" s="6" t="n">
+        <v>2.8244</v>
+      </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -4755,7 +4773,7 @@
         <v>-0.0493</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>-1.4765</v>
+        <v>0.02</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -4798,8 +4816,10 @@
       <c r="H97" s="6" t="n">
         <v>-0.08800000000000001</v>
       </c>
-      <c r="I97" s="6" t="n">
-        <v>0.7664</v>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>-1.940.81</t>
+        </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
@@ -4844,9 +4864,7 @@
       <c r="H98" s="3" t="n">
         <v>0.0435</v>
       </c>
-      <c r="I98" s="3" t="n">
-        <v>-0.8774999999999999</v>
-      </c>
+      <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -4888,7 +4906,9 @@
       <c r="H99" s="6" t="n">
         <v>-0.0398</v>
       </c>
-      <c r="I99" s="5" t="inlineStr"/>
+      <c r="I99" s="6" t="n">
+        <v>-2.9215</v>
+      </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -4931,7 +4951,7 @@
         <v>-0.019</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>-1.269</v>
+        <v>-4.305400000000001</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -4974,9 +4994,7 @@
       <c r="H101" s="6" t="n">
         <v>-0.0146</v>
       </c>
-      <c r="I101" s="6" t="n">
-        <v>-1.4555</v>
-      </c>
+      <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -5021,7 +5039,7 @@
         <v>0.0475</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>-0.578</v>
+        <v>-1.9014</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -5065,7 +5083,7 @@
         <v>-0.1172</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>0.5004999999999999</v>
+        <v>-4.7257</v>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
@@ -5110,8 +5128,10 @@
       <c r="H104" s="3" t="n">
         <v>0.007800000000000001</v>
       </c>
-      <c r="I104" s="3" t="n">
-        <v>-0.7723</v>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-11.313.82</t>
+        </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -5155,7 +5175,7 @@
         <v>-0.176</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>-6.4742</v>
+        <v>0.7059000000000001</v>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
@@ -5198,9 +5218,7 @@
       <c r="H106" s="3" t="n">
         <v>-0.1674</v>
       </c>
-      <c r="I106" s="3" t="n">
-        <v>-3.931</v>
-      </c>
+      <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
           <t>Enerji-dışı mineraller</t>
@@ -5245,7 +5263,7 @@
         <v>0.002</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>-0.9620000000000001</v>
+        <v>-3.8753</v>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
@@ -5289,7 +5307,7 @@
         <v>-0.09539999999999998</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>-0.3605</v>
+        <v>-0.5884</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -5332,11 +5350,7 @@
       <c r="H109" s="6" t="n">
         <v>-0.1204</v>
       </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>-1.357.95</t>
-        </is>
-      </c>
+      <c r="I109" s="5" t="inlineStr"/>
       <c r="J109" s="5" t="inlineStr">
         <is>
           <t>Enerji-dışı mineraller</t>
@@ -5379,7 +5393,7 @@
         <v>-0.0179</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>-1.2429</v>
+        <v>-2.4632</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -5469,7 +5483,7 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>-0.1668</v>
+        <v>-0.5133</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -5559,7 +5573,7 @@
         <v>0.1188</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0.9762000000000001</v>
+        <v>5.5933</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -5605,7 +5619,7 @@
         <v>0.0859</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>-0.07629999999999999</v>
+        <v>1.1742</v>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
@@ -5650,9 +5664,7 @@
       <c r="H116" s="3" t="n">
         <v>0.0926</v>
       </c>
-      <c r="I116" s="3" t="n">
-        <v>0.196</v>
-      </c>
+      <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr">
         <is>
           <t>Taşımacılık</t>
@@ -5697,7 +5709,7 @@
         <v>0.04219999999999999</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>-0.3061</v>
+        <v>1.93</v>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
@@ -5740,8 +5752,10 @@
       <c r="H118" s="3" t="n">
         <v>-0.1556</v>
       </c>
-      <c r="I118" s="3" t="n">
-        <v>-2.3249</v>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>-1.874.90</t>
+        </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -5783,7 +5797,7 @@
       </c>
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="6" t="n">
-        <v>-8.773899999999999</v>
+        <v>-2.7704</v>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
@@ -5826,8 +5840,10 @@
       <c r="H120" s="3" t="n">
         <v>-0.103</v>
       </c>
-      <c r="I120" s="3" t="n">
-        <v>-5.3546</v>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>-1.205.13</t>
+        </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -5873,7 +5889,7 @@
         <v>0.2894</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>0.1078</v>
+        <v>-0.2844</v>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
@@ -5918,7 +5934,11 @@
       <c r="H122" s="3" t="n">
         <v>0.0793</v>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>+1.164.09</t>
+        </is>
+      </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
           <t>Perakende satış</t>
@@ -5961,7 +5981,7 @@
         <v>-0.1558</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>0.4878</v>
+        <v>-5.5493</v>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
@@ -6007,7 +6027,7 @@
         <v>0.6177</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>1.9107</v>
+        <v>1.5477</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -6052,10 +6072,8 @@
       <c r="H125" s="6" t="n">
         <v>0.0358</v>
       </c>
-      <c r="I125" s="5" t="inlineStr">
-        <is>
-          <t>+1.964.66</t>
-        </is>
+      <c r="I125" s="6" t="n">
+        <v>-0.0001</v>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
@@ -6098,9 +6116,7 @@
       <c r="H126" s="3" t="n">
         <v>-0.0447</v>
       </c>
-      <c r="I126" s="3" t="n">
-        <v>-1.3087</v>
-      </c>
+      <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr">
         <is>
           <t>Çeşitli Hizmetler</t>
@@ -6145,7 +6161,7 @@
         <v>0.0475</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>-0.3374</v>
+        <v>-1.4654</v>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
@@ -6191,7 +6207,7 @@
         <v>0.0293</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>-0.4481</v>
+        <v>5.0381</v>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
@@ -6237,7 +6253,7 @@
         <v>0.0349</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>-0.431</v>
+        <v>1.1795</v>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
@@ -6281,7 +6297,7 @@
         <v>-0.0207</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>-1.0871</v>
+        <v>-1.5031</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -6324,7 +6340,9 @@
       <c r="H131" s="6" t="n">
         <v>0.1267</v>
       </c>
-      <c r="I131" s="5" t="inlineStr"/>
+      <c r="I131" s="6" t="n">
+        <v>-0.3898</v>
+      </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
           <t>Çeşitli Hizmetler</t>
@@ -6369,7 +6387,7 @@
         <v>0.1434</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>0.035</v>
+        <v>-0.9609000000000001</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6431,7 @@
         <v>-0.1411</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>-5.5185</v>
+        <v>-8.579000000000001</v>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
@@ -6458,9 +6476,7 @@
       <c r="H134" s="3" t="n">
         <v>0.07679999999999999</v>
       </c>
-      <c r="I134" s="3" t="n">
-        <v>0.9033</v>
-      </c>
+      <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
           <t>Dayanıklı tüketim malları</t>
@@ -6501,7 +6517,7 @@
         <v>0.1819</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>0.4905</v>
+        <v>0.6855</v>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
@@ -6545,7 +6561,7 @@
         <v>-0.06370000000000001</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>-0.0174</v>
+        <v>-2.6374</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -6591,7 +6607,7 @@
         <v>0.0488</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>-0.627</v>
+        <v>-3.3307</v>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
@@ -6635,7 +6651,7 @@
         <v>-0.0105</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>-1.1661</v>
+        <v>-1.102</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -6680,7 +6696,9 @@
       <c r="H139" s="6" t="n">
         <v>0.2876</v>
       </c>
-      <c r="I139" s="5" t="inlineStr"/>
+      <c r="I139" s="6" t="n">
+        <v>-8.504899999999999</v>
+      </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -6725,7 +6743,7 @@
         <v>0.0808</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>1.3436</v>
+        <v>0.3223</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -6769,7 +6787,7 @@
         <v>-0.1607</v>
       </c>
       <c r="I141" s="6" t="n">
-        <v>-0.4778</v>
+        <v>-3.4952</v>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
@@ -6814,7 +6832,9 @@
       <c r="H142" s="3" t="n">
         <v>0.0182</v>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="I142" s="3" t="n">
+        <v>8.0586</v>
+      </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -6856,8 +6876,10 @@
       <c r="H143" s="6" t="n">
         <v>-0.0184</v>
       </c>
-      <c r="I143" s="6" t="n">
-        <v>-2.0514</v>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>-1.832.47</t>
+        </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
@@ -6898,7 +6920,9 @@
         <v>0.008100000000000001</v>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr"/>
+      <c r="I144" s="3" t="n">
+        <v>0.1822</v>
+      </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -6941,7 +6965,7 @@
         <v>-0.0721</v>
       </c>
       <c r="I145" s="6" t="n">
-        <v>-6.1312</v>
+        <v>0.7347</v>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
@@ -6987,7 +7011,7 @@
         <v>0.0146</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>-0.3327000000000001</v>
+        <v>0.1293</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -7031,7 +7055,7 @@
         <v>-0.2495</v>
       </c>
       <c r="I147" s="6" t="n">
-        <v>-3.4318</v>
+        <v>-1.6467</v>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
@@ -7077,7 +7101,7 @@
         <v>0.05309999999999999</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>-0.1006</v>
+        <v>-2.7441</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -7123,7 +7147,7 @@
         <v>0.0463</v>
       </c>
       <c r="I149" s="6" t="n">
-        <v>-0.5711999999999999</v>
+        <v>-0.068</v>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
@@ -7167,7 +7191,7 @@
         <v>-0.0231</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>0.4384</v>
+        <v>-0.0625</v>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -7211,7 +7235,7 @@
         <v>-0.0102</v>
       </c>
       <c r="I151" s="6" t="n">
-        <v>0.2638</v>
+        <v>1.099</v>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
@@ -7255,7 +7279,7 @@
         <v>-0.0451</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>-3.4486</v>
+        <v>-5.186900000000001</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -7300,9 +7324,7 @@
       <c r="H153" s="6" t="n">
         <v>0.076</v>
       </c>
-      <c r="I153" s="6" t="n">
-        <v>-0.1492</v>
-      </c>
+      <c r="I153" s="5" t="inlineStr"/>
       <c r="J153" s="5" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -7344,10 +7366,8 @@
       <c r="H154" s="3" t="n">
         <v>-0.0576</v>
       </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>-2.763.43</t>
-        </is>
+      <c r="I154" s="3" t="n">
+        <v>-6.3558</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -7391,7 +7411,7 @@
         <v>-0.131</v>
       </c>
       <c r="I155" s="6" t="n">
-        <v>0.5841</v>
+        <v>-4.6418</v>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
@@ -7436,10 +7456,8 @@
       <c r="H156" s="3" t="n">
         <v>0.0941</v>
       </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>+1.036.24</t>
-        </is>
+      <c r="I156" s="3" t="n">
+        <v>-0.5928</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -7484,7 +7502,9 @@
       <c r="H157" s="6" t="n">
         <v>0.077</v>
       </c>
-      <c r="I157" s="5" t="inlineStr"/>
+      <c r="I157" s="6" t="n">
+        <v>-1.2862</v>
+      </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
           <t>Teknoloji hizmetleri</t>
@@ -7529,7 +7549,7 @@
         <v>0.07629999999999999</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>0.207</v>
+        <v>-0.2259</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -7575,7 +7595,7 @@
         <v>0.299</v>
       </c>
       <c r="I159" s="6" t="n">
-        <v>-0.1219</v>
+        <v>-0.0136</v>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
@@ -7618,10 +7638,8 @@
       <c r="H160" s="3" t="n">
         <v>-0.1779</v>
       </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>-1.494.47</t>
-        </is>
+      <c r="I160" s="3" t="n">
+        <v>-9.995900000000001</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -7665,7 +7683,7 @@
         <v>-0.1566</v>
       </c>
       <c r="I161" s="6" t="n">
-        <v>-1.5739</v>
+        <v>0.7471</v>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
@@ -7708,9 +7726,7 @@
       <c r="H162" s="3" t="n">
         <v>-0.0042</v>
       </c>
-      <c r="I162" s="3" t="n">
-        <v>-1.0734</v>
-      </c>
+      <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -7754,7 +7770,11 @@
       <c r="H163" s="6" t="n">
         <v>0.0636</v>
       </c>
-      <c r="I163" s="5" t="inlineStr"/>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>+15.614.26</t>
+        </is>
+      </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
           <t>Endüstriyel hizmetler</t>
@@ -7797,7 +7817,7 @@
         <v>-1.1835</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>-5.2964</v>
+        <v>-1.1923</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -7840,9 +7860,7 @@
       <c r="H165" s="6" t="n">
         <v>-0.0406</v>
       </c>
-      <c r="I165" s="6" t="n">
-        <v>-9.8714</v>
-      </c>
+      <c r="I165" s="5" t="inlineStr"/>
       <c r="J165" s="5" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -7887,7 +7905,7 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>-0.2507</v>
+        <v>-2.2043</v>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
@@ -7932,7 +7950,9 @@
       <c r="H167" s="6" t="n">
         <v>0.039</v>
       </c>
-      <c r="I167" s="5" t="inlineStr"/>
+      <c r="I167" s="6" t="n">
+        <v>2.881</v>
+      </c>
       <c r="J167" s="5" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -7977,7 +7997,7 @@
         <v>0.0873</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>-0.3104</v>
+        <v>-1.5011</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -8023,7 +8043,7 @@
         <v>0.2783</v>
       </c>
       <c r="I169" s="6" t="n">
-        <v>0.5685</v>
+        <v>1.0588</v>
       </c>
       <c r="J169" s="5" t="inlineStr">
         <is>
@@ -8067,7 +8087,7 @@
         <v>-0.0902</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>-3.5595</v>
+        <v>-0.5942000000000001</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
@@ -8111,7 +8131,7 @@
         <v>-0.1156</v>
       </c>
       <c r="I171" s="6" t="n">
-        <v>-5.8009</v>
+        <v>0.0659</v>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
@@ -8157,7 +8177,7 @@
         <v>0.1769</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>0.1206</v>
+        <v>1.394</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
@@ -8203,7 +8223,7 @@
         <v>0.1222</v>
       </c>
       <c r="I173" s="6" t="n">
-        <v>1.6895</v>
+        <v>-0.8391</v>
       </c>
       <c r="J173" s="5" t="inlineStr">
         <is>
@@ -8291,7 +8311,7 @@
         <v>-0.2143</v>
       </c>
       <c r="I175" s="6" t="n">
-        <v>-2.6285</v>
+        <v>-4.419</v>
       </c>
       <c r="J175" s="5" t="inlineStr">
         <is>
@@ -8334,8 +8354,10 @@
       <c r="H176" s="3" t="n">
         <v>-0.0344</v>
       </c>
-      <c r="I176" s="3" t="n">
-        <v>-1.0833</v>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>+2.714.10</t>
+        </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
@@ -8380,7 +8402,9 @@
       <c r="H177" s="6" t="n">
         <v>0.2011</v>
       </c>
-      <c r="I177" s="5" t="inlineStr"/>
+      <c r="I177" s="6" t="n">
+        <v>0.6818000000000001</v>
+      </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -8424,7 +8448,9 @@
       <c r="H178" s="3" t="n">
         <v>0.1155</v>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
+      <c r="I178" s="3" t="n">
+        <v>0.1014</v>
+      </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -8467,7 +8493,7 @@
         <v>-0.4584</v>
       </c>
       <c r="I179" s="6" t="n">
-        <v>-0.2456</v>
+        <v>-0.3601</v>
       </c>
       <c r="J179" s="5" t="inlineStr">
         <is>
@@ -8511,7 +8537,7 @@
         <v>-0.0553</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>-3.8669</v>
+        <v>-7.0937</v>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
@@ -8555,7 +8581,7 @@
         <v>-0.1373</v>
       </c>
       <c r="I181" s="6" t="n">
-        <v>0.4425</v>
+        <v>0.8694</v>
       </c>
       <c r="J181" s="5" t="inlineStr">
         <is>
@@ -8644,9 +8670,7 @@
       <c r="H183" s="6" t="n">
         <v>0.2405</v>
       </c>
-      <c r="I183" s="6" t="n">
-        <v>1.9359</v>
-      </c>
+      <c r="I183" s="5" t="inlineStr"/>
       <c r="J183" s="5" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -8691,7 +8715,7 @@
         <v>0.0737</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>0.6984999999999999</v>
+        <v>-1.8749</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -8737,7 +8761,7 @@
         <v>0.1202</v>
       </c>
       <c r="I185" s="6" t="n">
-        <v>-0.3499</v>
+        <v>-0.7368000000000001</v>
       </c>
       <c r="J185" s="5" t="inlineStr">
         <is>
@@ -8782,9 +8806,7 @@
       <c r="H186" s="3" t="n">
         <v>0.0323</v>
       </c>
-      <c r="I186" s="3" t="n">
-        <v>-0.078</v>
-      </c>
+      <c r="I186" s="2" t="inlineStr"/>
       <c r="J186" s="2" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -8830,7 +8852,9 @@
       <c r="H187" s="6" t="n">
         <v>0.0002</v>
       </c>
-      <c r="I187" s="5" t="inlineStr"/>
+      <c r="I187" s="6" t="n">
+        <v>-2.3862</v>
+      </c>
       <c r="J187" s="5" t="inlineStr">
         <is>
           <t>Ticari hizmetler</t>
@@ -8873,7 +8897,7 @@
         <v>-0.3417</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>-6.3988</v>
+        <v>-2.1476</v>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
@@ -8918,7 +8942,9 @@
       <c r="H189" s="6" t="n">
         <v>0.0354</v>
       </c>
-      <c r="I189" s="5" t="inlineStr"/>
+      <c r="I189" s="6" t="n">
+        <v>-6.6864</v>
+      </c>
       <c r="J189" s="5" t="inlineStr">
         <is>
           <t>Taşımacılık</t>
@@ -8961,7 +8987,7 @@
         <v>-0.8428</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>-1.5069</v>
+        <v>-1.2716</v>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
@@ -9006,7 +9032,7 @@
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>-3.916.21</t>
+          <t>-1.646.77</t>
         </is>
       </c>
       <c r="J191" s="5" t="inlineStr">
@@ -9053,7 +9079,7 @@
         <v>0.07629999999999999</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>0.3007</v>
+        <v>2.0964</v>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
@@ -9098,9 +9124,7 @@
       <c r="H193" s="6" t="n">
         <v>0.0508</v>
       </c>
-      <c r="I193" s="6" t="n">
-        <v>-0.5219</v>
-      </c>
+      <c r="I193" s="5" t="inlineStr"/>
       <c r="J193" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -9145,7 +9169,7 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>0.6601</v>
+        <v>0.6942</v>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
@@ -9191,7 +9215,7 @@
         <v>0.026</v>
       </c>
       <c r="I195" s="6" t="n">
-        <v>-0.8217</v>
+        <v>-0.1098</v>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
@@ -9234,9 +9258,7 @@
       <c r="H196" s="3" t="n">
         <v>-0.4141</v>
       </c>
-      <c r="I196" s="3" t="n">
-        <v>-0.5146000000000001</v>
-      </c>
+      <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -9279,7 +9301,7 @@
         <v>-0.0451</v>
       </c>
       <c r="I197" s="6" t="n">
-        <v>-1.6948</v>
+        <v>-1.622</v>
       </c>
       <c r="J197" s="5" t="inlineStr">
         <is>
@@ -9324,7 +9346,9 @@
       <c r="H198" s="3" t="n">
         <v>0.0253</v>
       </c>
-      <c r="I198" s="2" t="inlineStr"/>
+      <c r="I198" s="3" t="n">
+        <v>2.3941</v>
+      </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -9368,8 +9392,10 @@
       <c r="H199" s="6" t="n">
         <v>0.06860000000000001</v>
       </c>
-      <c r="I199" s="6" t="n">
-        <v>1.328</v>
+      <c r="I199" s="5" t="inlineStr">
+        <is>
+          <t>+1.634.04</t>
+        </is>
       </c>
       <c r="J199" s="5" t="inlineStr">
         <is>
@@ -9413,7 +9439,7 @@
         <v>-0.3344</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>-0.7983</v>
+        <v>0.7206999999999999</v>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
@@ -9459,7 +9485,7 @@
         <v>0.2395</v>
       </c>
       <c r="I201" s="6" t="n">
-        <v>0.2234</v>
+        <v>0.4835</v>
       </c>
       <c r="J201" s="5" t="inlineStr">
         <is>
@@ -9503,7 +9529,7 @@
         <v>-0.2839</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>-0.5984</v>
+        <v>-4.2686</v>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
@@ -9547,7 +9573,7 @@
         <v>-0.0342</v>
       </c>
       <c r="I203" s="6" t="n">
-        <v>0.5058</v>
+        <v>0.1735</v>
       </c>
       <c r="J203" s="5" t="inlineStr">
         <is>
@@ -9591,7 +9617,7 @@
         <v>-0.1716</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>-8.369899999999999</v>
+        <v>-2.2777</v>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
@@ -9637,7 +9663,7 @@
         <v>0.5625</v>
       </c>
       <c r="I205" s="6" t="n">
-        <v>9.7545</v>
+        <v>4.1559</v>
       </c>
       <c r="J205" s="5" t="inlineStr">
         <is>
@@ -9683,7 +9709,7 @@
         <v>0.099</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>-0.424</v>
+        <v>2.5821</v>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
@@ -9771,7 +9797,7 @@
         <v>-0.5577000000000001</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>-4.1306</v>
+        <v>0.3825</v>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
@@ -9814,9 +9840,7 @@
       <c r="H209" s="6" t="n">
         <v>-0.0213</v>
       </c>
-      <c r="I209" s="6" t="n">
-        <v>-1.2446</v>
-      </c>
+      <c r="I209" s="5" t="inlineStr"/>
       <c r="J209" s="5" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -9857,7 +9881,7 @@
         <v>0.0738</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>0.9397</v>
+        <v>2.8209</v>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
@@ -9901,7 +9925,7 @@
         <v>-0.0635</v>
       </c>
       <c r="I211" s="6" t="n">
-        <v>0.4361</v>
+        <v>-0.0447</v>
       </c>
       <c r="J211" s="5" t="inlineStr">
         <is>
@@ -9945,7 +9969,7 @@
         <v>-0.1669</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>-1.2692</v>
+        <v>-8.9087</v>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
@@ -9990,10 +10014,8 @@
       <c r="H213" s="6" t="n">
         <v>0.1271</v>
       </c>
-      <c r="I213" s="5" t="inlineStr">
-        <is>
-          <t>+1.663.75</t>
-        </is>
+      <c r="I213" s="6" t="n">
+        <v>0.2388</v>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
@@ -10036,10 +10058,8 @@
       <c r="H214" s="3" t="n">
         <v>-0.1749</v>
       </c>
-      <c r="I214" s="2" t="inlineStr">
-        <is>
-          <t>-1.326.24</t>
-        </is>
+      <c r="I214" s="3" t="n">
+        <v>-2.1565</v>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
@@ -10084,7 +10104,9 @@
       <c r="H215" s="6" t="n">
         <v>0.0595</v>
       </c>
-      <c r="I215" s="5" t="inlineStr"/>
+      <c r="I215" s="6" t="n">
+        <v>0.9056999999999999</v>
+      </c>
       <c r="J215" s="5" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -10127,7 +10149,7 @@
         <v>-0.0149</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>-1.4557</v>
+        <v>-6.0927</v>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
@@ -10173,7 +10195,7 @@
         <v>0.06559999999999999</v>
       </c>
       <c r="I217" s="6" t="n">
-        <v>0.0343</v>
+        <v>-0.6212</v>
       </c>
       <c r="J217" s="5" t="inlineStr">
         <is>
@@ -10221,7 +10243,7 @@
         <v>0.0008</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>-0.9715</v>
+        <v>1.5318</v>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
@@ -10265,7 +10287,7 @@
         <v>-0.0486</v>
       </c>
       <c r="I219" s="6" t="n">
-        <v>-4.7939</v>
+        <v>-2.9048</v>
       </c>
       <c r="J219" s="5" t="inlineStr">
         <is>
@@ -10347,7 +10369,7 @@
         <v>0.3469</v>
       </c>
       <c r="I221" s="6" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.1967</v>
       </c>
       <c r="J221" s="5" t="inlineStr">
         <is>
@@ -10391,7 +10413,7 @@
         <v>-0.3776</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>-1.93</v>
+        <v>-5.3326</v>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
@@ -10437,7 +10459,7 @@
         <v>0.21</v>
       </c>
       <c r="I223" s="6" t="n">
-        <v>0.6229</v>
+        <v>-0.3839</v>
       </c>
       <c r="J223" s="5" t="inlineStr">
         <is>
@@ -10483,7 +10505,7 @@
         <v>0.0968</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>-0.4342</v>
+        <v>0.7339</v>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
@@ -10529,7 +10551,7 @@
         <v>0.0546</v>
       </c>
       <c r="I225" s="6" t="n">
-        <v>-0.2419</v>
+        <v>-0.8634000000000001</v>
       </c>
       <c r="J225" s="5" t="inlineStr">
         <is>
@@ -10574,7 +10596,9 @@
       <c r="H226" s="3" t="n">
         <v>0.2569</v>
       </c>
-      <c r="I226" s="2" t="inlineStr"/>
+      <c r="I226" s="3" t="n">
+        <v>2.5615</v>
+      </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -10614,7 +10638,11 @@
         <v>0.0116</v>
       </c>
       <c r="H227" s="5" t="inlineStr"/>
-      <c r="I227" s="5" t="inlineStr"/>
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>+6.814.51</t>
+        </is>
+      </c>
       <c r="J227" s="5" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -10659,7 +10687,7 @@
         <v>0.1008</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>3.4572</v>
+        <v>1.4774</v>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
@@ -10749,7 +10777,7 @@
         <v>0.208</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>0.3514</v>
+        <v>0.3034</v>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
@@ -10793,7 +10821,7 @@
         <v>-0.235</v>
       </c>
       <c r="I231" s="6" t="n">
-        <v>-3.7094</v>
+        <v>-4.909800000000001</v>
       </c>
       <c r="J231" s="5" t="inlineStr">
         <is>
@@ -10838,9 +10866,7 @@
       <c r="H232" s="3" t="n">
         <v>0.0344</v>
       </c>
-      <c r="I232" s="3" t="n">
-        <v>1.5971</v>
-      </c>
+      <c r="I232" s="2" t="inlineStr"/>
       <c r="J232" s="2" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -10885,7 +10911,7 @@
         <v>0.2319</v>
       </c>
       <c r="I233" s="6" t="n">
-        <v>-0.07440000000000001</v>
+        <v>0.9412</v>
       </c>
       <c r="J233" s="5" t="inlineStr">
         <is>
@@ -10929,7 +10955,7 @@
         <v>-0.0693</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>-1.887</v>
+        <v>-9.6821</v>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
@@ -10975,7 +11001,7 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I235" s="6" t="n">
-        <v>1.8263</v>
+        <v>-0.8061</v>
       </c>
       <c r="J235" s="5" t="inlineStr">
         <is>
@@ -11023,7 +11049,7 @@
         <v>0.0005</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>-0.9895</v>
+        <v>-5.5053</v>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
@@ -11069,7 +11095,7 @@
         <v>0.0293</v>
       </c>
       <c r="I237" s="6" t="n">
-        <v>-0.6698000000000001</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="J237" s="5" t="inlineStr">
         <is>
@@ -11113,7 +11139,7 @@
         <v>-0.1012</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>-2.2531</v>
+        <v>-5.8898</v>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
@@ -11159,7 +11185,7 @@
         <v>0.141</v>
       </c>
       <c r="I239" s="6" t="n">
-        <v>0.2311</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="J239" s="5" t="inlineStr">
         <is>
@@ -11205,7 +11231,7 @@
         <v>0.035</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>0.9035</v>
+        <v>-1.9718</v>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11277,7 @@
         <v>0.2528</v>
       </c>
       <c r="I241" s="6" t="n">
-        <v>2.0469</v>
+        <v>-2.0563</v>
       </c>
       <c r="J241" s="5" t="inlineStr">
         <is>
@@ -11295,7 +11321,7 @@
         <v>-0.1484</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>0.0823</v>
+        <v>-5.3684</v>
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
@@ -11341,7 +11367,7 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I243" s="6" t="n">
-        <v>0.1579</v>
+        <v>6.779</v>
       </c>
       <c r="J243" s="5" t="inlineStr">
         <is>
@@ -11386,7 +11412,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>-1.520.66</t>
+          <t>-10.598.33</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
@@ -11432,9 +11458,7 @@
       <c r="H245" s="6" t="n">
         <v>0.0159</v>
       </c>
-      <c r="I245" s="6" t="n">
-        <v>-0.1918</v>
-      </c>
+      <c r="I245" s="5" t="inlineStr"/>
       <c r="J245" s="5" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -11479,7 +11503,7 @@
         <v>0.2838</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>0.2036</v>
+        <v>-0.1339</v>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
@@ -11525,7 +11549,7 @@
         <v>0.1261</v>
       </c>
       <c r="I247" s="6" t="n">
-        <v>0.4551</v>
+        <v>1.3131</v>
       </c>
       <c r="J247" s="5" t="inlineStr">
         <is>
@@ -11571,7 +11595,7 @@
         <v>0.0178</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>1.7524</v>
+        <v>-2.3758</v>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
@@ -11617,7 +11641,7 @@
         <v>0.4074</v>
       </c>
       <c r="I249" s="6" t="n">
-        <v>-0.167</v>
+        <v>0.5552</v>
       </c>
       <c r="J249" s="5" t="inlineStr">
         <is>
@@ -11663,7 +11687,7 @@
         <v>0.0415</v>
       </c>
       <c r="I250" s="3" t="n">
-        <v>-0.7654000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
@@ -11707,7 +11731,7 @@
         <v>-0.1903</v>
       </c>
       <c r="I251" s="6" t="n">
-        <v>-0.9225</v>
+        <v>-1.1628</v>
       </c>
       <c r="J251" s="5" t="inlineStr">
         <is>
@@ -11752,7 +11776,9 @@
       <c r="H252" s="3" t="n">
         <v>0.0639</v>
       </c>
-      <c r="I252" s="2" t="inlineStr"/>
+      <c r="I252" s="3" t="n">
+        <v>0.2738</v>
+      </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -11795,7 +11821,7 @@
         <v>-0.0319</v>
       </c>
       <c r="I253" s="6" t="n">
-        <v>0.6535</v>
+        <v>0.0693</v>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
@@ -11840,8 +11866,10 @@
       <c r="H254" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="I254" s="3" t="n">
-        <v>1.4453</v>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>+1.147.15</t>
+        </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
@@ -11887,7 +11915,7 @@
         <v>0.0311</v>
       </c>
       <c r="I255" s="6" t="n">
-        <v>0.7168000000000001</v>
+        <v>-1.456</v>
       </c>
       <c r="J255" s="5" t="inlineStr">
         <is>
@@ -11931,7 +11959,7 @@
         <v>-0.1673</v>
       </c>
       <c r="I256" s="3" t="n">
-        <v>-1.3067</v>
+        <v>-5.3873</v>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
@@ -11976,8 +12004,10 @@
       <c r="H257" s="6" t="n">
         <v>0.231</v>
       </c>
-      <c r="I257" s="6" t="n">
-        <v>7.204800000000001</v>
+      <c r="I257" s="5" t="inlineStr">
+        <is>
+          <t>+1.371.51</t>
+        </is>
       </c>
       <c r="J257" s="5" t="inlineStr">
         <is>
@@ -12021,7 +12051,7 @@
         <v>-0.1771</v>
       </c>
       <c r="I258" s="3" t="n">
-        <v>-0.426</v>
+        <v>0.7664</v>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
@@ -12064,9 +12094,7 @@
       <c r="H259" s="6" t="n">
         <v>-0.0272</v>
       </c>
-      <c r="I259" s="6" t="n">
-        <v>-1.6174</v>
-      </c>
+      <c r="I259" s="5" t="inlineStr"/>
       <c r="J259" s="5" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -12111,7 +12139,7 @@
         <v>0.1409</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>2.9348</v>
+        <v>-0.3902</v>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
@@ -12157,7 +12185,7 @@
         <v>0.0044</v>
       </c>
       <c r="I261" s="6" t="n">
-        <v>-0.7447</v>
+        <v>-1.293</v>
       </c>
       <c r="J261" s="5" t="inlineStr">
         <is>
@@ -12200,9 +12228,7 @@
       <c r="H262" s="3" t="n">
         <v>-0.0683</v>
       </c>
-      <c r="I262" s="3" t="n">
-        <v>0.151</v>
-      </c>
+      <c r="I262" s="2" t="inlineStr"/>
       <c r="J262" s="2" t="inlineStr">
         <is>
           <t>Enerji-dışı mineraller</t>
@@ -12247,7 +12273,7 @@
         <v>0.08929999999999999</v>
       </c>
       <c r="I263" s="6" t="n">
-        <v>0.6194</v>
+        <v>-0.3668</v>
       </c>
       <c r="J263" s="5" t="inlineStr">
         <is>
@@ -12293,7 +12319,7 @@
         <v>0.121</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>0.023</v>
+        <v>3.3313</v>
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12362,8 @@
       <c r="H265" s="6" t="n">
         <v>-0.04389999999999999</v>
       </c>
-      <c r="I265" s="5" t="inlineStr">
-        <is>
-          <t>-1.089.42</t>
-        </is>
+      <c r="I265" s="6" t="n">
+        <v>-1.3459</v>
       </c>
       <c r="J265" s="5" t="inlineStr">
         <is>
@@ -12385,7 +12409,7 @@
         <v>0.1162</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>0.4675</v>
+        <v>-0.2881</v>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
@@ -12429,7 +12453,7 @@
         <v>-0.1422</v>
       </c>
       <c r="I267" s="6" t="n">
-        <v>0.5196000000000001</v>
+        <v>0.5267000000000001</v>
       </c>
       <c r="J267" s="5" t="inlineStr">
         <is>
@@ -12475,7 +12499,7 @@
         <v>0.1527</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>-0.0689</v>
+        <v>0.2796</v>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
@@ -12521,7 +12545,7 @@
         <v>0.0668</v>
       </c>
       <c r="I269" s="6" t="n">
-        <v>-0.3608</v>
+        <v>0.0314</v>
       </c>
       <c r="J269" s="5" t="inlineStr">
         <is>
@@ -12565,7 +12589,7 @@
         <v>-0.1117</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>-0.8586</v>
+        <v>6.849</v>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
@@ -12609,7 +12633,7 @@
         <v>-0.0183</v>
       </c>
       <c r="I271" s="6" t="n">
-        <v>-1.0951</v>
+        <v>-2.2684</v>
       </c>
       <c r="J271" s="5" t="inlineStr">
         <is>
@@ -12654,7 +12678,9 @@
       <c r="H272" s="3" t="n">
         <v>0.05</v>
       </c>
-      <c r="I272" s="2" t="inlineStr"/>
+      <c r="I272" s="3" t="n">
+        <v>-0.2381</v>
+      </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -12697,7 +12723,7 @@
         <v>-0.01</v>
       </c>
       <c r="I273" s="6" t="n">
-        <v>-2.4539</v>
+        <v>0.0576</v>
       </c>
       <c r="J273" s="5" t="inlineStr">
         <is>
@@ -12741,7 +12767,7 @@
         <v>-0.2936</v>
       </c>
       <c r="I274" s="3" t="n">
-        <v>-1.9173</v>
+        <v>-2.2139</v>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12813,7 @@
         <v>0.0925</v>
       </c>
       <c r="I275" s="6" t="n">
-        <v>0.0403</v>
+        <v>-0.722</v>
       </c>
       <c r="J275" s="5" t="inlineStr">
         <is>
@@ -12830,9 +12856,7 @@
       <c r="H276" s="3" t="n">
         <v>-0.3044</v>
       </c>
-      <c r="I276" s="3" t="n">
-        <v>0.1989</v>
-      </c>
+      <c r="I276" s="2" t="inlineStr"/>
       <c r="J276" s="2" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -12877,7 +12901,7 @@
         <v>0.1039</v>
       </c>
       <c r="I277" s="6" t="n">
-        <v>0.2002</v>
+        <v>-0.4064</v>
       </c>
       <c r="J277" s="5" t="inlineStr">
         <is>
@@ -12923,7 +12947,7 @@
         <v>0.0336</v>
       </c>
       <c r="I278" s="3" t="n">
-        <v>0.3468</v>
+        <v>-1.3921</v>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
@@ -12966,8 +12990,10 @@
       <c r="H279" s="6" t="n">
         <v>-0.0406</v>
       </c>
-      <c r="I279" s="6" t="n">
-        <v>-1.3178</v>
+      <c r="I279" s="5" t="inlineStr">
+        <is>
+          <t>-1.129.33</t>
+        </is>
       </c>
       <c r="J279" s="5" t="inlineStr">
         <is>
@@ -13013,7 +13039,7 @@
         <v>0.4054</v>
       </c>
       <c r="I280" s="3" t="n">
-        <v>0.4754</v>
+        <v>0.2344</v>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
@@ -13058,8 +13084,10 @@
       <c r="H281" s="6" t="n">
         <v>0.006500000000000001</v>
       </c>
-      <c r="I281" s="6" t="n">
-        <v>-0.9533</v>
+      <c r="I281" s="5" t="inlineStr">
+        <is>
+          <t>+32.859.73</t>
+        </is>
       </c>
       <c r="J281" s="5" t="inlineStr">
         <is>
@@ -13103,7 +13131,7 @@
         <v>-0.0675</v>
       </c>
       <c r="I282" s="3" t="n">
-        <v>0.6394</v>
+        <v>-3.2771</v>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
@@ -13149,7 +13177,7 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I283" s="6" t="n">
-        <v>1.6592</v>
+        <v>0.701</v>
       </c>
       <c r="J283" s="5" t="inlineStr">
         <is>
@@ -13195,7 +13223,7 @@
         <v>0.1767</v>
       </c>
       <c r="I284" s="3" t="n">
-        <v>-0.1383</v>
+        <v>0.8362999999999999</v>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
@@ -13241,7 +13269,7 @@
         <v>0.4531</v>
       </c>
       <c r="I285" s="6" t="n">
-        <v>0.164</v>
+        <v>0.197</v>
       </c>
       <c r="J285" s="5" t="inlineStr">
         <is>
@@ -13286,7 +13314,9 @@
       <c r="H286" s="3" t="n">
         <v>0.038</v>
       </c>
-      <c r="I286" s="2" t="inlineStr"/>
+      <c r="I286" s="3" t="n">
+        <v>2.6888</v>
+      </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -13330,9 +13360,7 @@
       <c r="H287" s="6" t="n">
         <v>0.009000000000000001</v>
       </c>
-      <c r="I287" s="6" t="n">
-        <v>-0.8602</v>
-      </c>
+      <c r="I287" s="5" t="inlineStr"/>
       <c r="J287" s="5" t="inlineStr">
         <is>
           <t>Dayanıklı tüketim malları</t>
@@ -13373,7 +13401,7 @@
         <v>0.0408</v>
       </c>
       <c r="I288" s="3" t="n">
-        <v>-0.5706</v>
+        <v>-1.203</v>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
@@ -13419,7 +13447,7 @@
         <v>0.1109</v>
       </c>
       <c r="I289" s="6" t="n">
-        <v>0.4655</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="J289" s="5" t="inlineStr">
         <is>
@@ -13464,7 +13492,9 @@
       <c r="H290" s="3" t="n">
         <v>0.4519</v>
       </c>
-      <c r="I290" s="2" t="inlineStr"/>
+      <c r="I290" s="3" t="n">
+        <v>0.8454</v>
+      </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -13507,7 +13537,7 @@
         <v>-0.0742</v>
       </c>
       <c r="I291" s="6" t="n">
-        <v>0.5636</v>
+        <v>0.5233</v>
       </c>
       <c r="J291" s="5" t="inlineStr">
         <is>
@@ -13551,7 +13581,7 @@
         <v>-0.0219</v>
       </c>
       <c r="I292" s="3" t="n">
-        <v>-1.5005</v>
+        <v>0.8834000000000001</v>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
@@ -13597,7 +13627,7 @@
         <v>0.0322</v>
       </c>
       <c r="I293" s="6" t="n">
-        <v>-0.5452</v>
+        <v>-0.4215</v>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
@@ -13643,7 +13673,7 @@
         <v>0.1088</v>
       </c>
       <c r="I294" s="3" t="n">
-        <v>-0.1548</v>
+        <v>-0.4633</v>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
@@ -13686,8 +13716,10 @@
       <c r="H295" s="6" t="n">
         <v>-0.0292</v>
       </c>
-      <c r="I295" s="6" t="n">
-        <v>-1.2088</v>
+      <c r="I295" s="5" t="inlineStr">
+        <is>
+          <t>-1.850.72</t>
+        </is>
       </c>
       <c r="J295" s="5" t="inlineStr">
         <is>
@@ -13730,7 +13762,11 @@
       <c r="H296" s="3" t="n">
         <v>-0.08710000000000001</v>
       </c>
-      <c r="I296" s="2" t="inlineStr"/>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>-1.799.59</t>
+        </is>
+      </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -13774,11 +13810,7 @@
       <c r="H297" s="6" t="n">
         <v>0.4496</v>
       </c>
-      <c r="I297" s="5" t="inlineStr">
-        <is>
-          <t>+1.742.89</t>
-        </is>
-      </c>
+      <c r="I297" s="5" t="inlineStr"/>
       <c r="J297" s="5" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -13819,7 +13851,7 @@
         <v>0.0338</v>
       </c>
       <c r="I298" s="3" t="n">
-        <v>-0.5886</v>
+        <v>-0.6236999999999999</v>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
@@ -13907,7 +13939,7 @@
         <v>-0.3168</v>
       </c>
       <c r="I300" s="3" t="n">
-        <v>-9.002699999999999</v>
+        <v>-2.0753</v>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
@@ -13951,7 +13983,7 @@
         <v>-0.0104</v>
       </c>
       <c r="I301" s="6" t="n">
-        <v>-1.1285</v>
+        <v>-2.9114</v>
       </c>
       <c r="J301" s="5" t="inlineStr">
         <is>
@@ -13995,7 +14027,7 @@
         <v>-0.0232</v>
       </c>
       <c r="I302" s="3" t="n">
-        <v>-1.2608</v>
+        <v>1.6493</v>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
@@ -14041,7 +14073,7 @@
         <v>-0.0123</v>
       </c>
       <c r="I303" s="6" t="n">
-        <v>-1.993</v>
+        <v>-3.2424</v>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
@@ -14084,7 +14116,9 @@
       <c r="H304" s="3" t="n">
         <v>-0.0906</v>
       </c>
-      <c r="I304" s="2" t="inlineStr"/>
+      <c r="I304" s="3" t="n">
+        <v>-4.0218</v>
+      </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -14129,7 +14163,7 @@
         <v>0.344</v>
       </c>
       <c r="I305" s="6" t="n">
-        <v>3.3959</v>
+        <v>1.5455</v>
       </c>
       <c r="J305" s="5" t="inlineStr">
         <is>
@@ -14175,7 +14209,7 @@
         <v>0.1964</v>
       </c>
       <c r="I306" s="3" t="n">
-        <v>1.3926</v>
+        <v>4.1859</v>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
@@ -14221,7 +14255,7 @@
         <v>0.0704</v>
       </c>
       <c r="I307" s="6" t="n">
-        <v>0.9468000000000001</v>
+        <v>0.2988</v>
       </c>
       <c r="J307" s="5" t="inlineStr">
         <is>
@@ -14267,7 +14301,7 @@
         <v>0.09720000000000001</v>
       </c>
       <c r="I308" s="3" t="n">
-        <v>-0.121</v>
+        <v>-0.8568000000000001</v>
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
@@ -14313,7 +14347,7 @@
         <v>0.2919</v>
       </c>
       <c r="I309" s="6" t="n">
-        <v>0.1813</v>
+        <v>0.233</v>
       </c>
       <c r="J309" s="5" t="inlineStr">
         <is>
@@ -14359,7 +14393,7 @@
         <v>0.0888</v>
       </c>
       <c r="I310" s="3" t="n">
-        <v>-0.4828</v>
+        <v>-0.2047</v>
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
@@ -14402,7 +14436,9 @@
       <c r="H311" s="6" t="n">
         <v>0.3377000000000001</v>
       </c>
-      <c r="I311" s="5" t="inlineStr"/>
+      <c r="I311" s="6" t="n">
+        <v>-0.0438</v>
+      </c>
       <c r="J311" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -14447,7 +14483,7 @@
         <v>0.0051</v>
       </c>
       <c r="I312" s="3" t="n">
-        <v>-0.8377</v>
+        <v>-3.014</v>
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
@@ -14493,7 +14529,7 @@
         <v>0.121</v>
       </c>
       <c r="I313" s="6" t="n">
-        <v>-0.4613</v>
+        <v>-0.3443</v>
       </c>
       <c r="J313" s="5" t="inlineStr">
         <is>
@@ -14536,7 +14572,9 @@
       <c r="H314" s="3" t="n">
         <v>0.008100000000000001</v>
       </c>
-      <c r="I314" s="2" t="inlineStr"/>
+      <c r="I314" s="3" t="n">
+        <v>4.8334</v>
+      </c>
       <c r="J314" s="2" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -14581,7 +14619,7 @@
         <v>0.0946</v>
       </c>
       <c r="I315" s="6" t="n">
-        <v>1.8716</v>
+        <v>0.2596</v>
       </c>
       <c r="J315" s="5" t="inlineStr">
         <is>
@@ -14625,7 +14663,7 @@
         <v>0.1521</v>
       </c>
       <c r="I316" s="3" t="n">
-        <v>1.2824</v>
+        <v>7.5378</v>
       </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
@@ -14668,9 +14706,7 @@
       <c r="H317" s="6" t="n">
         <v>-0.0133</v>
       </c>
-      <c r="I317" s="6" t="n">
-        <v>-1.1778</v>
-      </c>
+      <c r="I317" s="5" t="inlineStr"/>
       <c r="J317" s="5" t="inlineStr">
         <is>
           <t>Dağıtım servisleri</t>
@@ -14757,7 +14793,7 @@
         <v>-0.101</v>
       </c>
       <c r="I319" s="6" t="n">
-        <v>-2.695</v>
+        <v>-0.2884</v>
       </c>
       <c r="J319" s="5" t="inlineStr">
         <is>
@@ -14803,7 +14839,7 @@
         <v>0.0669</v>
       </c>
       <c r="I320" s="3" t="n">
-        <v>0.6221</v>
+        <v>4.7457</v>
       </c>
       <c r="J320" s="2" t="inlineStr">
         <is>
@@ -14849,7 +14885,7 @@
         <v>0.1712</v>
       </c>
       <c r="I321" s="6" t="n">
-        <v>0.8012999999999999</v>
+        <v>0.8176000000000001</v>
       </c>
       <c r="J321" s="5" t="inlineStr">
         <is>
@@ -14895,7 +14931,7 @@
         <v>0.0393</v>
       </c>
       <c r="I322" s="3" t="n">
-        <v>5.895599999999999</v>
+        <v>0.0506</v>
       </c>
       <c r="J322" s="2" t="inlineStr">
         <is>
@@ -14939,7 +14975,7 @@
         <v>-0.1471</v>
       </c>
       <c r="I323" s="6" t="n">
-        <v>-0.1423</v>
+        <v>0.0029</v>
       </c>
       <c r="J323" s="5" t="inlineStr">
         <is>
@@ -14982,7 +15018,9 @@
       <c r="H324" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="I324" s="2" t="inlineStr"/>
+      <c r="I324" s="3" t="n">
+        <v>0.2025</v>
+      </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>Elektronik teknoloji</t>
@@ -15027,7 +15065,7 @@
         <v>0.2928</v>
       </c>
       <c r="I325" s="6" t="n">
-        <v>1.0055</v>
+        <v>0.6712</v>
       </c>
       <c r="J325" s="5" t="inlineStr">
         <is>
@@ -15072,8 +15110,10 @@
       <c r="H326" s="3" t="n">
         <v>0.0358</v>
       </c>
-      <c r="I326" s="3" t="n">
-        <v>2.4305</v>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>+2.796.08</t>
+        </is>
       </c>
       <c r="J326" s="2" t="inlineStr">
         <is>
@@ -15119,7 +15159,7 @@
         <v>0.0885</v>
       </c>
       <c r="I327" s="6" t="n">
-        <v>0.3228</v>
+        <v>-0.0863</v>
       </c>
       <c r="J327" s="5" t="inlineStr">
         <is>
@@ -15159,7 +15199,7 @@
         <v>-0.2826</v>
       </c>
       <c r="I328" s="3" t="n">
-        <v>-0.4976</v>
+        <v>-0.3658</v>
       </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
@@ -15249,7 +15289,7 @@
         <v>0.9309000000000001</v>
       </c>
       <c r="I330" s="3" t="n">
-        <v>6.6751</v>
+        <v>2.8984</v>
       </c>
       <c r="J330" s="2" t="inlineStr">
         <is>
@@ -15293,7 +15333,7 @@
         <v>-0.0123</v>
       </c>
       <c r="I331" s="6" t="n">
-        <v>-1.7613</v>
+        <v>-3.104</v>
       </c>
       <c r="J331" s="5" t="inlineStr">
         <is>
@@ -15339,7 +15379,7 @@
         <v>0.132</v>
       </c>
       <c r="I332" s="3" t="n">
-        <v>0.2085</v>
+        <v>0.0143</v>
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
@@ -15383,7 +15423,7 @@
         <v>-0.213</v>
       </c>
       <c r="I333" s="6" t="n">
-        <v>-7.182799999999999</v>
+        <v>0.5029</v>
       </c>
       <c r="J333" s="5" t="inlineStr">
         <is>
@@ -15426,8 +15466,10 @@
       <c r="H334" s="3" t="n">
         <v>-0.1453</v>
       </c>
-      <c r="I334" s="3" t="n">
-        <v>-1.0553</v>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>-31.319.14</t>
+        </is>
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
@@ -15472,9 +15514,7 @@
       <c r="H335" s="6" t="n">
         <v>0.0318</v>
       </c>
-      <c r="I335" s="6" t="n">
-        <v>-0.6417</v>
-      </c>
+      <c r="I335" s="5" t="inlineStr"/>
       <c r="J335" s="5" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -15517,7 +15557,7 @@
         <v>-0.0375</v>
       </c>
       <c r="I336" s="3" t="n">
-        <v>-1.1668</v>
+        <v>0.6358</v>
       </c>
       <c r="J336" s="2" t="inlineStr">
         <is>
@@ -15560,8 +15600,10 @@
       <c r="H337" s="6" t="n">
         <v>-0.2085</v>
       </c>
-      <c r="I337" s="6" t="n">
-        <v>-2.6206</v>
+      <c r="I337" s="5" t="inlineStr">
+        <is>
+          <t>-1.048.42</t>
+        </is>
       </c>
       <c r="J337" s="5" t="inlineStr">
         <is>
@@ -15607,7 +15649,7 @@
         <v>0.1553</v>
       </c>
       <c r="I338" s="3" t="n">
-        <v>0.2338</v>
+        <v>-0.5638000000000001</v>
       </c>
       <c r="J338" s="2" t="inlineStr">
         <is>
@@ -15653,7 +15695,7 @@
         <v>0.0863</v>
       </c>
       <c r="I339" s="6" t="n">
-        <v>1.5966</v>
+        <v>5.7455</v>
       </c>
       <c r="J339" s="5" t="inlineStr">
         <is>
@@ -15699,7 +15741,7 @@
         <v>0.2423</v>
       </c>
       <c r="I340" s="3" t="n">
-        <v>0.3489</v>
+        <v>0.7472</v>
       </c>
       <c r="J340" s="2" t="inlineStr">
         <is>
@@ -15779,7 +15821,7 @@
         <v>-0.0332</v>
       </c>
       <c r="I342" s="3" t="n">
-        <v>-2.1342</v>
+        <v>-0.8992</v>
       </c>
       <c r="J342" s="2" t="inlineStr">
         <is>
@@ -15824,7 +15866,9 @@
       <c r="H343" s="6" t="n">
         <v>0.2608</v>
       </c>
-      <c r="I343" s="5" t="inlineStr"/>
+      <c r="I343" s="6" t="n">
+        <v>6.3451</v>
+      </c>
       <c r="J343" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -15867,7 +15911,7 @@
         <v>-0.4183</v>
       </c>
       <c r="I344" s="3" t="n">
-        <v>-0.8679000000000001</v>
+        <v>-1.6177</v>
       </c>
       <c r="J344" s="2" t="inlineStr">
         <is>
@@ -15910,7 +15954,9 @@
       <c r="H345" s="6" t="n">
         <v>-0.06150000000000001</v>
       </c>
-      <c r="I345" s="5" t="inlineStr"/>
+      <c r="I345" s="6" t="n">
+        <v>-1.6584</v>
+      </c>
       <c r="J345" s="5" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -15955,7 +16001,7 @@
         <v>0.0416</v>
       </c>
       <c r="I346" s="3" t="n">
-        <v>-0.9417</v>
+        <v>0.9954999999999999</v>
       </c>
       <c r="J346" s="2" t="inlineStr">
         <is>
@@ -15994,9 +16040,7 @@
       <c r="H347" s="6" t="n">
         <v>-0.09710000000000001</v>
       </c>
-      <c r="I347" s="6" t="n">
-        <v>-0.0135</v>
-      </c>
+      <c r="I347" s="5" t="inlineStr"/>
       <c r="J347" s="5" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -16039,7 +16083,7 @@
         <v>-0.1527</v>
       </c>
       <c r="I348" s="3" t="n">
-        <v>-4.8074</v>
+        <v>-4.6508</v>
       </c>
       <c r="J348" s="2" t="inlineStr">
         <is>
@@ -16125,7 +16169,7 @@
         <v>-0.9107</v>
       </c>
       <c r="I350" s="3" t="n">
-        <v>-1.5264</v>
+        <v>-3.7217</v>
       </c>
       <c r="J350" s="2" t="inlineStr">
         <is>
@@ -16171,7 +16215,7 @@
         <v>0.157</v>
       </c>
       <c r="I351" s="6" t="n">
-        <v>-0.1727</v>
+        <v>-1.2844</v>
       </c>
       <c r="J351" s="5" t="inlineStr">
         <is>
@@ -16216,7 +16260,9 @@
       <c r="H352" s="3" t="n">
         <v>0.0375</v>
       </c>
-      <c r="I352" s="2" t="inlineStr"/>
+      <c r="I352" s="3" t="n">
+        <v>-1.2803</v>
+      </c>
       <c r="J352" s="2" t="inlineStr">
         <is>
           <t>Enerji-dışı mineraller</t>
@@ -16260,7 +16306,9 @@
       <c r="H353" s="6" t="n">
         <v>0.09080000000000001</v>
       </c>
-      <c r="I353" s="5" t="inlineStr"/>
+      <c r="I353" s="6" t="n">
+        <v>-1.3787</v>
+      </c>
       <c r="J353" s="5" t="inlineStr">
         <is>
           <t>Enerji-dışı mineraller</t>
@@ -16303,7 +16351,7 @@
         <v>-0.1212</v>
       </c>
       <c r="I354" s="3" t="n">
-        <v>-0.7568</v>
+        <v>0.7595999999999999</v>
       </c>
       <c r="J354" s="2" t="inlineStr">
         <is>
@@ -16346,8 +16394,10 @@
       <c r="H355" s="6" t="n">
         <v>-0.1306</v>
       </c>
-      <c r="I355" s="6" t="n">
-        <v>-1.4591</v>
+      <c r="I355" s="5" t="inlineStr">
+        <is>
+          <t>-5.331.43</t>
+        </is>
       </c>
       <c r="J355" s="5" t="inlineStr">
         <is>
@@ -16391,7 +16441,7 @@
         <v>-1.0324</v>
       </c>
       <c r="I356" s="3" t="n">
-        <v>-2.4292</v>
+        <v>-0.2257</v>
       </c>
       <c r="J356" s="2" t="inlineStr">
         <is>
@@ -16436,7 +16486,9 @@
       <c r="H357" s="6" t="n">
         <v>0.0216</v>
       </c>
-      <c r="I357" s="5" t="inlineStr"/>
+      <c r="I357" s="6" t="n">
+        <v>-1.4265</v>
+      </c>
       <c r="J357" s="5" t="inlineStr">
         <is>
           <t>Enerji mineralleri</t>
@@ -16481,7 +16533,7 @@
         <v>0.4401</v>
       </c>
       <c r="I358" s="3" t="n">
-        <v>0.5349</v>
+        <v>3.6517</v>
       </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
@@ -16526,7 +16578,9 @@
       <c r="H359" s="6" t="n">
         <v>0.04190000000000001</v>
       </c>
-      <c r="I359" s="5" t="inlineStr"/>
+      <c r="I359" s="6" t="n">
+        <v>3.7407</v>
+      </c>
       <c r="J359" s="5" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -16568,10 +16622,8 @@
       <c r="H360" s="3" t="n">
         <v>-0.2756</v>
       </c>
-      <c r="I360" s="2" t="inlineStr">
-        <is>
-          <t>-1.807.61</t>
-        </is>
+      <c r="I360" s="3" t="n">
+        <v>0.5871999999999999</v>
       </c>
       <c r="J360" s="2" t="inlineStr">
         <is>
@@ -16617,7 +16669,7 @@
         <v>0.5025999999999999</v>
       </c>
       <c r="I361" s="6" t="n">
-        <v>0.4812</v>
+        <v>-0.121</v>
       </c>
       <c r="J361" s="5" t="inlineStr">
         <is>
@@ -16661,7 +16713,7 @@
         <v>-0.2545</v>
       </c>
       <c r="I362" s="3" t="n">
-        <v>0.5607</v>
+        <v>-0.5023</v>
       </c>
       <c r="J362" s="2" t="inlineStr">
         <is>
@@ -16707,7 +16759,7 @@
         <v>0.3184</v>
       </c>
       <c r="I363" s="6" t="n">
-        <v>-0.0264</v>
+        <v>-0.1897</v>
       </c>
       <c r="J363" s="5" t="inlineStr">
         <is>
@@ -16752,7 +16804,9 @@
       <c r="H364" s="3" t="n">
         <v>0.1128</v>
       </c>
-      <c r="I364" s="2" t="inlineStr"/>
+      <c r="I364" s="3" t="n">
+        <v>-0.9066</v>
+      </c>
       <c r="J364" s="2" t="inlineStr">
         <is>
           <t>Perakende satış</t>
@@ -16842,7 +16896,9 @@
       <c r="H366" s="3" t="n">
         <v>0.0154</v>
       </c>
-      <c r="I366" s="2" t="inlineStr"/>
+      <c r="I366" s="3" t="n">
+        <v>-0.8693000000000001</v>
+      </c>
       <c r="J366" s="2" t="inlineStr">
         <is>
           <t>Perakende satış</t>
@@ -16887,7 +16943,7 @@
         <v>0.0073</v>
       </c>
       <c r="I367" s="6" t="n">
-        <v>-0.9063</v>
+        <v>-0.3059</v>
       </c>
       <c r="J367" s="5" t="inlineStr">
         <is>
@@ -16933,7 +16989,7 @@
         <v>0.08449999999999999</v>
       </c>
       <c r="I368" s="3" t="n">
-        <v>-0.1569</v>
+        <v>0.1882</v>
       </c>
       <c r="J368" s="2" t="inlineStr">
         <is>
@@ -16976,8 +17032,10 @@
       <c r="H369" s="6" t="n">
         <v>-0.057</v>
       </c>
-      <c r="I369" s="6" t="n">
-        <v>-1.5497</v>
+      <c r="I369" s="5" t="inlineStr">
+        <is>
+          <t>-1.961.93</t>
+        </is>
       </c>
       <c r="J369" s="5" t="inlineStr">
         <is>
@@ -17021,7 +17079,7 @@
         <v>-0.0423</v>
       </c>
       <c r="I370" s="3" t="n">
-        <v>-1.4357</v>
+        <v>0.1053</v>
       </c>
       <c r="J370" s="2" t="inlineStr">
         <is>
@@ -17111,7 +17169,7 @@
         <v>0.3117</v>
       </c>
       <c r="I372" s="3" t="n">
-        <v>0.9319</v>
+        <v>0.7249</v>
       </c>
       <c r="J372" s="2" t="inlineStr">
         <is>
@@ -17155,7 +17213,7 @@
         <v>-0.5177</v>
       </c>
       <c r="I373" s="6" t="n">
-        <v>0.0295</v>
+        <v>-2.3054</v>
       </c>
       <c r="J373" s="5" t="inlineStr">
         <is>
@@ -17198,8 +17256,10 @@
       <c r="H374" s="3" t="n">
         <v>-0.1176</v>
       </c>
-      <c r="I374" s="3" t="n">
-        <v>-4.124</v>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>-1.937.98</t>
+        </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
         <is>
@@ -17243,7 +17303,7 @@
         <v>-0.1977</v>
       </c>
       <c r="I375" s="6" t="n">
-        <v>-9.1616</v>
+        <v>-0.0043</v>
       </c>
       <c r="J375" s="5" t="inlineStr">
         <is>
@@ -17287,7 +17347,7 @@
         <v>-0.0684</v>
       </c>
       <c r="I376" s="3" t="n">
-        <v>0.201</v>
+        <v>-1.9324</v>
       </c>
       <c r="J376" s="2" t="inlineStr">
         <is>
@@ -17328,8 +17388,10 @@
       <c r="H377" s="6" t="n">
         <v>-0.0145</v>
       </c>
-      <c r="I377" s="6" t="n">
-        <v>-1.1282</v>
+      <c r="I377" s="5" t="inlineStr">
+        <is>
+          <t>-1.327.04</t>
+        </is>
       </c>
       <c r="J377" s="5" t="inlineStr">
         <is>
@@ -17373,7 +17435,7 @@
         <v>-0.0029</v>
       </c>
       <c r="I378" s="3" t="n">
-        <v>-1.2042</v>
+        <v>-3.8066</v>
       </c>
       <c r="J378" s="2" t="inlineStr">
         <is>
@@ -17419,7 +17481,7 @@
         <v>0.1539</v>
       </c>
       <c r="I379" s="6" t="n">
-        <v>0.792</v>
+        <v>3.4881</v>
       </c>
       <c r="J379" s="5" t="inlineStr">
         <is>
@@ -17462,9 +17524,7 @@
       <c r="H380" s="3" t="n">
         <v>-0.2194</v>
       </c>
-      <c r="I380" s="3" t="n">
-        <v>-3.5664</v>
-      </c>
+      <c r="I380" s="2" t="inlineStr"/>
       <c r="J380" s="2" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -17507,7 +17567,7 @@
         <v>-0.098</v>
       </c>
       <c r="I381" s="6" t="n">
-        <v>0.7093</v>
+        <v>2.4746</v>
       </c>
       <c r="J381" s="5" t="inlineStr">
         <is>
@@ -17553,7 +17613,7 @@
         <v>0.1095</v>
       </c>
       <c r="I382" s="3" t="n">
-        <v>-0.238</v>
+        <v>-0.2312</v>
       </c>
       <c r="J382" s="2" t="inlineStr">
         <is>
@@ -17599,7 +17659,7 @@
         <v>0.2405</v>
       </c>
       <c r="I383" s="6" t="n">
-        <v>-0.1113</v>
+        <v>0.3834</v>
       </c>
       <c r="J383" s="5" t="inlineStr">
         <is>
@@ -17645,7 +17705,7 @@
         <v>0.1897</v>
       </c>
       <c r="I384" s="3" t="n">
-        <v>5.680800000000001</v>
+        <v>-0.3458</v>
       </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
@@ -17690,7 +17750,9 @@
       <c r="H385" s="6" t="n">
         <v>0.0633</v>
       </c>
-      <c r="I385" s="5" t="inlineStr"/>
+      <c r="I385" s="6" t="n">
+        <v>-0.2432</v>
+      </c>
       <c r="J385" s="5" t="inlineStr">
         <is>
           <t>Perakende satış</t>
@@ -17735,7 +17797,7 @@
         <v>0.1843</v>
       </c>
       <c r="I386" s="3" t="n">
-        <v>-0.048</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="J386" s="2" t="inlineStr">
         <is>
@@ -17781,7 +17843,7 @@
         <v>0.458</v>
       </c>
       <c r="I387" s="6" t="n">
-        <v>0.2676</v>
+        <v>-0.1093</v>
       </c>
       <c r="J387" s="5" t="inlineStr">
         <is>
@@ -17824,8 +17886,10 @@
       <c r="H388" s="3" t="n">
         <v>-0.0582</v>
       </c>
-      <c r="I388" s="3" t="n">
-        <v>-3.5233</v>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>-1.550.87</t>
+        </is>
       </c>
       <c r="J388" s="2" t="inlineStr">
         <is>
@@ -17868,9 +17932,7 @@
       <c r="H389" s="6" t="n">
         <v>-0.0267</v>
       </c>
-      <c r="I389" s="6" t="n">
-        <v>0.2044</v>
-      </c>
+      <c r="I389" s="5" t="inlineStr"/>
       <c r="J389" s="5" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -17915,7 +17977,7 @@
         <v>0.0294</v>
       </c>
       <c r="I390" s="3" t="n">
-        <v>0.0547</v>
+        <v>-2.2136</v>
       </c>
       <c r="J390" s="2" t="inlineStr">
         <is>
@@ -17961,7 +18023,7 @@
         <v>0.1794</v>
       </c>
       <c r="I391" s="6" t="n">
-        <v>-0.1385</v>
+        <v>-0.9131999999999999</v>
       </c>
       <c r="J391" s="5" t="inlineStr">
         <is>
@@ -18004,8 +18066,10 @@
       <c r="H392" s="3" t="n">
         <v>-0.057</v>
       </c>
-      <c r="I392" s="3" t="n">
-        <v>-2.1156</v>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>-2.283.80</t>
+        </is>
       </c>
       <c r="J392" s="2" t="inlineStr">
         <is>
@@ -18049,7 +18113,7 @@
         <v>-0.6525</v>
       </c>
       <c r="I393" s="6" t="n">
-        <v>-2.0716</v>
+        <v>-2.2369</v>
       </c>
       <c r="J393" s="5" t="inlineStr">
         <is>
@@ -18094,10 +18158,8 @@
       <c r="H394" s="3" t="n">
         <v>1.1538</v>
       </c>
-      <c r="I394" s="2" t="inlineStr">
-        <is>
-          <t>+23.677.45</t>
-        </is>
+      <c r="I394" s="3" t="n">
+        <v>1.7569</v>
       </c>
       <c r="J394" s="2" t="inlineStr">
         <is>
@@ -18142,7 +18204,9 @@
       <c r="H395" s="6" t="n">
         <v>0.0575</v>
       </c>
-      <c r="I395" s="5" t="inlineStr"/>
+      <c r="I395" s="6" t="n">
+        <v>-1.8265</v>
+      </c>
       <c r="J395" s="5" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -18185,7 +18249,7 @@
         <v>-0.0159</v>
       </c>
       <c r="I396" s="3" t="n">
-        <v>-1.0539</v>
+        <v>-0.9540000000000001</v>
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
@@ -18231,7 +18295,7 @@
         <v>0.1275</v>
       </c>
       <c r="I397" s="6" t="n">
-        <v>0.0326</v>
+        <v>0.399</v>
       </c>
       <c r="J397" s="5" t="inlineStr">
         <is>
@@ -18277,7 +18341,7 @@
         <v>0.2087</v>
       </c>
       <c r="I398" s="3" t="n">
-        <v>-0.0235</v>
+        <v>-0.9989</v>
       </c>
       <c r="J398" s="2" t="inlineStr">
         <is>
@@ -18322,8 +18386,10 @@
           <t>-3.347.85</t>
         </is>
       </c>
-      <c r="I399" s="6" t="n">
-        <v>-3.1283</v>
+      <c r="I399" s="5" t="inlineStr">
+        <is>
+          <t>-1.431.12</t>
+        </is>
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
@@ -18368,9 +18434,7 @@
       <c r="H400" s="3" t="n">
         <v>0.0177</v>
       </c>
-      <c r="I400" s="3" t="n">
-        <v>2.9694</v>
-      </c>
+      <c r="I400" s="2" t="inlineStr"/>
       <c r="J400" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -18458,9 +18522,7 @@
       <c r="H402" s="3" t="n">
         <v>0.2008</v>
       </c>
-      <c r="I402" s="3" t="n">
-        <v>4.6931</v>
-      </c>
+      <c r="I402" s="2" t="inlineStr"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
           <t>Teknoloji hizmetleri</t>
@@ -18504,7 +18566,9 @@
       <c r="H403" s="6" t="n">
         <v>0.454</v>
       </c>
-      <c r="I403" s="5" t="inlineStr"/>
+      <c r="I403" s="6" t="n">
+        <v>-0.7884</v>
+      </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
           <t>Teknoloji hizmetleri</t>
@@ -18546,10 +18610,8 @@
       <c r="H404" s="3" t="n">
         <v>-0.1323</v>
       </c>
-      <c r="I404" s="2" t="inlineStr">
-        <is>
-          <t>-1.185.83</t>
-        </is>
+      <c r="I404" s="3" t="n">
+        <v>-0.3689</v>
       </c>
       <c r="J404" s="2" t="inlineStr">
         <is>
@@ -18595,7 +18657,7 @@
         <v>0.1577</v>
       </c>
       <c r="I405" s="6" t="n">
-        <v>-0.0241</v>
+        <v>0.8172</v>
       </c>
       <c r="J405" s="5" t="inlineStr">
         <is>
@@ -18641,7 +18703,7 @@
         <v>0.5052</v>
       </c>
       <c r="I406" s="3" t="n">
-        <v>0.5279</v>
+        <v>0.0187</v>
       </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
@@ -18685,7 +18747,7 @@
         <v>-0.0545</v>
       </c>
       <c r="I407" s="6" t="n">
-        <v>-3.9748</v>
+        <v>0.4473</v>
       </c>
       <c r="J407" s="5" t="inlineStr">
         <is>
@@ -18728,9 +18790,7 @@
       <c r="H408" s="3" t="n">
         <v>-0.09390000000000001</v>
       </c>
-      <c r="I408" s="3" t="n">
-        <v>-1.9513</v>
-      </c>
+      <c r="I408" s="2" t="inlineStr"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
           <t>Elektronik teknoloji</t>
@@ -18774,7 +18834,9 @@
       <c r="H409" s="6" t="n">
         <v>0.3585</v>
       </c>
-      <c r="I409" s="5" t="inlineStr"/>
+      <c r="I409" s="6" t="n">
+        <v>-0.5128</v>
+      </c>
       <c r="J409" s="5" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -18819,7 +18881,7 @@
         <v>0.0795</v>
       </c>
       <c r="I410" s="3" t="n">
-        <v>0.2873</v>
+        <v>-0.9063</v>
       </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18926,8 @@
       <c r="H411" s="6" t="n">
         <v>0.1475</v>
       </c>
-      <c r="I411" s="5" t="inlineStr">
-        <is>
-          <t>+1.313.34</t>
-        </is>
+      <c r="I411" s="6" t="n">
+        <v>-0.7215</v>
       </c>
       <c r="J411" s="5" t="inlineStr">
         <is>
@@ -18913,7 +18973,7 @@
         <v>0.1333</v>
       </c>
       <c r="I412" s="3" t="n">
-        <v>0.4166</v>
+        <v>6.844600000000001</v>
       </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
@@ -18959,7 +19019,7 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I413" s="6" t="n">
-        <v>1.7127</v>
+        <v>-1.0812</v>
       </c>
       <c r="J413" s="5" t="inlineStr">
         <is>
@@ -19002,9 +19062,7 @@
       <c r="H414" s="3" t="n">
         <v>-0.0027</v>
       </c>
-      <c r="I414" s="3" t="n">
-        <v>-1.057</v>
-      </c>
+      <c r="I414" s="2" t="inlineStr"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -19049,7 +19107,7 @@
         <v>0.2016</v>
       </c>
       <c r="I415" s="6" t="n">
-        <v>0.2214</v>
+        <v>0.5552</v>
       </c>
       <c r="J415" s="5" t="inlineStr">
         <is>
@@ -19092,8 +19150,10 @@
       <c r="H416" s="3" t="n">
         <v>-0.1769</v>
       </c>
-      <c r="I416" s="3" t="n">
-        <v>-1.2003</v>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>-52.884.46</t>
+        </is>
       </c>
       <c r="J416" s="2" t="inlineStr">
         <is>
@@ -19135,7 +19195,7 @@
         <v>0.1565</v>
       </c>
       <c r="I417" s="6" t="n">
-        <v>0.5357</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="J417" s="5" t="inlineStr">
         <is>
@@ -19181,7 +19241,7 @@
         <v>0.0235</v>
       </c>
       <c r="I418" s="3" t="n">
-        <v>-0.9245</v>
+        <v>-2.6291</v>
       </c>
       <c r="J418" s="2" t="inlineStr">
         <is>
@@ -19227,7 +19287,7 @@
         <v>0.0682</v>
       </c>
       <c r="I419" s="6" t="n">
-        <v>0.0633</v>
+        <v>-2.8727</v>
       </c>
       <c r="J419" s="5" t="inlineStr">
         <is>
@@ -19273,7 +19333,7 @@
         <v>0.1311</v>
       </c>
       <c r="I420" s="3" t="n">
-        <v>0.374</v>
+        <v>-0.8823000000000001</v>
       </c>
       <c r="J420" s="2" t="inlineStr">
         <is>
@@ -19318,9 +19378,7 @@
       <c r="H421" s="6" t="n">
         <v>0.2337</v>
       </c>
-      <c r="I421" s="6" t="n">
-        <v>0.2017</v>
-      </c>
+      <c r="I421" s="5" t="inlineStr"/>
       <c r="J421" s="5" t="inlineStr">
         <is>
           <t>Teknoloji hizmetleri</t>
@@ -19365,7 +19423,7 @@
         <v>0.2909</v>
       </c>
       <c r="I422" s="3" t="n">
-        <v>2.0552</v>
+        <v>2.7171</v>
       </c>
       <c r="J422" s="2" t="inlineStr">
         <is>
@@ -19451,7 +19509,7 @@
         <v>-0.005600000000000001</v>
       </c>
       <c r="I424" s="3" t="n">
-        <v>-1.0871</v>
+        <v>-0.7101999999999999</v>
       </c>
       <c r="J424" s="2" t="inlineStr">
         <is>
@@ -19494,10 +19552,8 @@
       <c r="H425" s="6" t="n">
         <v>-0.0958</v>
       </c>
-      <c r="I425" s="5" t="inlineStr">
-        <is>
-          <t>-1.722.54</t>
-        </is>
+      <c r="I425" s="6" t="n">
+        <v>-2.2418</v>
       </c>
       <c r="J425" s="5" t="inlineStr">
         <is>
@@ -19543,7 +19599,7 @@
         <v>0.6533</v>
       </c>
       <c r="I426" s="3" t="n">
-        <v>3.7752</v>
+        <v>-0.1442</v>
       </c>
       <c r="J426" s="2" t="inlineStr">
         <is>
@@ -19589,7 +19645,7 @@
         <v>0.3359</v>
       </c>
       <c r="I427" s="6" t="n">
-        <v>0.4585</v>
+        <v>0.07490000000000001</v>
       </c>
       <c r="J427" s="5" t="inlineStr">
         <is>
@@ -19631,7 +19687,7 @@
         <v>0.078</v>
       </c>
       <c r="I428" s="3" t="n">
-        <v>-0.491</v>
+        <v>-0.9328</v>
       </c>
       <c r="J428" s="2" t="inlineStr">
         <is>
@@ -19677,7 +19733,7 @@
         <v>0.1732</v>
       </c>
       <c r="I429" s="6" t="n">
-        <v>0.1985</v>
+        <v>8.039199999999999</v>
       </c>
       <c r="J429" s="5" t="inlineStr">
         <is>
@@ -19722,7 +19778,9 @@
       <c r="H430" s="3" t="n">
         <v>1.445</v>
       </c>
-      <c r="I430" s="2" t="inlineStr"/>
+      <c r="I430" s="3" t="n">
+        <v>-0.716</v>
+      </c>
       <c r="J430" s="2" t="inlineStr">
         <is>
           <t>Teknoloji hizmetleri</t>
@@ -19767,7 +19825,7 @@
         <v>0.3345</v>
       </c>
       <c r="I431" s="6" t="n">
-        <v>0.7881</v>
+        <v>0.6006</v>
       </c>
       <c r="J431" s="5" t="inlineStr">
         <is>
@@ -19810,10 +19868,8 @@
       <c r="H432" s="3" t="n">
         <v>-0.3911</v>
       </c>
-      <c r="I432" s="2" t="inlineStr">
-        <is>
-          <t>-3.485.75</t>
-        </is>
+      <c r="I432" s="3" t="n">
+        <v>-4.4402</v>
       </c>
       <c r="J432" s="2" t="inlineStr">
         <is>
@@ -19902,9 +19958,7 @@
       <c r="H434" s="3" t="n">
         <v>-0.0039</v>
       </c>
-      <c r="I434" s="3" t="n">
-        <v>-1.0509</v>
-      </c>
+      <c r="I434" s="2" t="inlineStr"/>
       <c r="J434" s="2" t="inlineStr">
         <is>
           <t>Elektronik teknoloji</t>
@@ -19948,9 +20002,7 @@
       <c r="H435" s="6" t="n">
         <v>0.0352</v>
       </c>
-      <c r="I435" s="6" t="n">
-        <v>0.0641</v>
-      </c>
+      <c r="I435" s="5" t="inlineStr"/>
       <c r="J435" s="5" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -19989,7 +20041,7 @@
         <v>-0.1171</v>
       </c>
       <c r="I436" s="3" t="n">
-        <v>-3.5326</v>
+        <v>-1.2976</v>
       </c>
       <c r="J436" s="2" t="inlineStr">
         <is>
@@ -20032,8 +20084,10 @@
       <c r="H437" s="6" t="n">
         <v>-0.0599</v>
       </c>
-      <c r="I437" s="6" t="n">
-        <v>0.3925</v>
+      <c r="I437" s="5" t="inlineStr">
+        <is>
+          <t>-4.484.91</t>
+        </is>
       </c>
       <c r="J437" s="5" t="inlineStr">
         <is>
@@ -20079,7 +20133,7 @@
         <v>0.1092</v>
       </c>
       <c r="I438" s="3" t="n">
-        <v>5.1637</v>
+        <v>-1.1669</v>
       </c>
       <c r="J438" s="2" t="inlineStr">
         <is>
@@ -20123,7 +20177,7 @@
         <v>-0.0576</v>
       </c>
       <c r="I439" s="6" t="n">
-        <v>-5.0708</v>
+        <v>-2.2771</v>
       </c>
       <c r="J439" s="5" t="inlineStr">
         <is>
@@ -20166,9 +20220,7 @@
       <c r="H440" s="3" t="n">
         <v>-0.0482</v>
       </c>
-      <c r="I440" s="3" t="n">
-        <v>0.2251</v>
-      </c>
+      <c r="I440" s="2" t="inlineStr"/>
       <c r="J440" s="2" t="inlineStr">
         <is>
           <t>Enerji-dışı mineraller</t>
@@ -20209,7 +20261,7 @@
         <v>0.248</v>
       </c>
       <c r="I441" s="6" t="n">
-        <v>1.1055</v>
+        <v>1.037</v>
       </c>
       <c r="J441" s="5" t="inlineStr">
         <is>
@@ -20253,7 +20305,7 @@
         <v>-0.1552</v>
       </c>
       <c r="I442" s="3" t="n">
-        <v>-0.5124</v>
+        <v>-0.45</v>
       </c>
       <c r="J442" s="2" t="inlineStr">
         <is>
@@ -20299,7 +20351,7 @@
         <v>0.4715</v>
       </c>
       <c r="I443" s="6" t="n">
-        <v>8.831900000000001</v>
+        <v>-0.4521</v>
       </c>
       <c r="J443" s="5" t="inlineStr">
         <is>
@@ -20345,7 +20397,7 @@
         <v>0.5052</v>
       </c>
       <c r="I444" s="3" t="n">
-        <v>0.3921</v>
+        <v>0.2386</v>
       </c>
       <c r="J444" s="2" t="inlineStr">
         <is>
@@ -20390,7 +20442,9 @@
       <c r="H445" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I445" s="5" t="inlineStr"/>
+      <c r="I445" s="6" t="n">
+        <v>0.5484</v>
+      </c>
       <c r="J445" s="5" t="inlineStr">
         <is>
           <t>Çeşitli Hizmetler</t>
@@ -20430,7 +20484,9 @@
       <c r="H446" s="3" t="n">
         <v>0.8473999999999999</v>
       </c>
-      <c r="I446" s="2" t="inlineStr"/>
+      <c r="I446" s="3" t="n">
+        <v>5.585199999999999</v>
+      </c>
       <c r="J446" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -20474,9 +20530,7 @@
       <c r="H447" s="6" t="n">
         <v>0.1656</v>
       </c>
-      <c r="I447" s="6" t="n">
-        <v>0.2451</v>
-      </c>
+      <c r="I447" s="5" t="inlineStr"/>
       <c r="J447" s="5" t="inlineStr">
         <is>
           <t>Ticari hizmetler</t>
@@ -20519,7 +20573,7 @@
         <v>-0.0142</v>
       </c>
       <c r="I448" s="3" t="n">
-        <v>-1.2837</v>
+        <v>-1.3835</v>
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
@@ -20611,7 +20665,7 @@
         <v>0.5835</v>
       </c>
       <c r="I450" s="3" t="n">
-        <v>0.6859999999999999</v>
+        <v>-0.4549</v>
       </c>
       <c r="J450" s="2" t="inlineStr">
         <is>
@@ -20655,7 +20709,7 @@
         <v>-0.4116</v>
       </c>
       <c r="I451" s="6" t="n">
-        <v>0.1703</v>
+        <v>-8.8185</v>
       </c>
       <c r="J451" s="5" t="inlineStr">
         <is>
@@ -20701,7 +20755,7 @@
         <v>0.1536</v>
       </c>
       <c r="I452" s="3" t="n">
-        <v>0.4045</v>
+        <v>-0.1008</v>
       </c>
       <c r="J452" s="2" t="inlineStr">
         <is>
@@ -20745,7 +20799,7 @@
         <v>-0.3138</v>
       </c>
       <c r="I453" s="6" t="n">
-        <v>-8.234400000000001</v>
+        <v>0.6631</v>
       </c>
       <c r="J453" s="5" t="inlineStr">
         <is>
@@ -20788,7 +20842,9 @@
       <c r="H454" s="3" t="n">
         <v>0.1652</v>
       </c>
-      <c r="I454" s="2" t="inlineStr"/>
+      <c r="I454" s="3" t="n">
+        <v>0.9714</v>
+      </c>
       <c r="J454" s="2" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -20833,7 +20889,7 @@
         <v>0.0644</v>
       </c>
       <c r="I455" s="6" t="n">
-        <v>-0.2565</v>
+        <v>1.3847</v>
       </c>
       <c r="J455" s="5" t="inlineStr">
         <is>
@@ -20877,7 +20933,7 @@
         <v>-0.1487</v>
       </c>
       <c r="I456" s="3" t="n">
-        <v>-1.3544</v>
+        <v>0.5216</v>
       </c>
       <c r="J456" s="2" t="inlineStr">
         <is>
@@ -20964,11 +21020,7 @@
       <c r="H458" s="3" t="n">
         <v>-0.0561</v>
       </c>
-      <c r="I458" s="2" t="inlineStr">
-        <is>
-          <t>-12.768.39</t>
-        </is>
-      </c>
+      <c r="I458" s="2" t="inlineStr"/>
       <c r="J458" s="2" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -21010,7 +21062,9 @@
       <c r="H459" s="6" t="n">
         <v>-0.0955</v>
       </c>
-      <c r="I459" s="5" t="inlineStr"/>
+      <c r="I459" s="6" t="n">
+        <v>-0.2029</v>
+      </c>
       <c r="J459" s="5" t="inlineStr">
         <is>
           <t>Elektrik. Su. Gaz Hizmetleri</t>
@@ -21053,7 +21107,7 @@
         <v>-0.0556</v>
       </c>
       <c r="I460" s="3" t="n">
-        <v>0.1954</v>
+        <v>-7.241000000000001</v>
       </c>
       <c r="J460" s="2" t="inlineStr">
         <is>
@@ -21097,7 +21151,7 @@
         <v>-0.0941</v>
       </c>
       <c r="I461" s="6" t="n">
-        <v>-2.8234</v>
+        <v>-1.7771</v>
       </c>
       <c r="J461" s="5" t="inlineStr">
         <is>
@@ -21143,7 +21197,7 @@
         <v>0.715</v>
       </c>
       <c r="I462" s="3" t="n">
-        <v>0.9097</v>
+        <v>-0.0185</v>
       </c>
       <c r="J462" s="2" t="inlineStr">
         <is>
@@ -21189,7 +21243,7 @@
         <v>0.2732</v>
       </c>
       <c r="I463" s="6" t="n">
-        <v>-0.1533</v>
+        <v>0.1278</v>
       </c>
       <c r="J463" s="5" t="inlineStr">
         <is>
@@ -21232,9 +21286,7 @@
       <c r="H464" s="3" t="n">
         <v>-0.0452</v>
       </c>
-      <c r="I464" s="3" t="n">
-        <v>0.2937</v>
-      </c>
+      <c r="I464" s="2" t="inlineStr"/>
       <c r="J464" s="2" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -21277,7 +21329,7 @@
         <v>-0.1367</v>
       </c>
       <c r="I465" s="6" t="n">
-        <v>-1.9165</v>
+        <v>-0.4155</v>
       </c>
       <c r="J465" s="5" t="inlineStr">
         <is>
@@ -21321,7 +21373,7 @@
         <v>-0.292</v>
       </c>
       <c r="I466" s="3" t="n">
-        <v>-2.4683</v>
+        <v>-3.2624</v>
       </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
@@ -21366,7 +21418,9 @@
       <c r="H467" s="6" t="n">
         <v>0.0728</v>
       </c>
-      <c r="I467" s="5" t="inlineStr"/>
+      <c r="I467" s="6" t="n">
+        <v>-0.0176</v>
+      </c>
       <c r="J467" s="5" t="inlineStr">
         <is>
           <t>Enerji-dışı mineraller</t>
@@ -21411,7 +21465,7 @@
         <v>0.2552</v>
       </c>
       <c r="I468" s="3" t="n">
-        <v>0.6668000000000001</v>
+        <v>0.2085</v>
       </c>
       <c r="J468" s="2" t="inlineStr">
         <is>
@@ -21457,7 +21511,7 @@
         <v>0.2892</v>
       </c>
       <c r="I469" s="6" t="n">
-        <v>0.9931</v>
+        <v>0.2476</v>
       </c>
       <c r="J469" s="5" t="inlineStr">
         <is>
@@ -21503,7 +21557,7 @@
         <v>0.5092</v>
       </c>
       <c r="I470" s="3" t="n">
-        <v>2.8938</v>
+        <v>-0.9779000000000001</v>
       </c>
       <c r="J470" s="2" t="inlineStr">
         <is>
@@ -21547,7 +21601,7 @@
         <v>-0.0173</v>
       </c>
       <c r="I471" s="6" t="n">
-        <v>-1.8474</v>
+        <v>0.6581999999999999</v>
       </c>
       <c r="J471" s="5" t="inlineStr">
         <is>
@@ -21591,7 +21645,7 @@
         <v>-0.0108</v>
       </c>
       <c r="I472" s="3" t="n">
-        <v>-1.3009</v>
+        <v>-0.3881</v>
       </c>
       <c r="J472" s="2" t="inlineStr">
         <is>
@@ -21633,7 +21687,7 @@
       </c>
       <c r="H473" s="5" t="inlineStr"/>
       <c r="I473" s="6" t="n">
-        <v>-1.1165</v>
+        <v>0.9449</v>
       </c>
       <c r="J473" s="5" t="inlineStr">
         <is>
@@ -21679,7 +21733,7 @@
         <v>1.3147</v>
       </c>
       <c r="I474" s="3" t="n">
-        <v>2.3196</v>
+        <v>-0.4052</v>
       </c>
       <c r="J474" s="2" t="inlineStr">
         <is>
@@ -21723,7 +21777,7 @@
         <v>-0.149</v>
       </c>
       <c r="I475" s="6" t="n">
-        <v>-7.3844</v>
+        <v>0.3441</v>
       </c>
       <c r="J475" s="5" t="inlineStr">
         <is>
@@ -21763,7 +21817,7 @@
         <v>-0.016</v>
       </c>
       <c r="I476" s="3" t="n">
-        <v>0.2327</v>
+        <v>-2.6951</v>
       </c>
       <c r="J476" s="2" t="inlineStr">
         <is>
@@ -21809,7 +21863,7 @@
         <v>0.4548</v>
       </c>
       <c r="I477" s="6" t="n">
-        <v>0.7468</v>
+        <v>-0.06860000000000001</v>
       </c>
       <c r="J477" s="5" t="inlineStr">
         <is>
@@ -21855,7 +21909,7 @@
         <v>0.1283</v>
       </c>
       <c r="I478" s="3" t="n">
-        <v>-0.1675</v>
+        <v>-0.5074000000000001</v>
       </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
@@ -21899,7 +21953,7 @@
         <v>-0.2073</v>
       </c>
       <c r="I479" s="6" t="n">
-        <v>-1.0044</v>
+        <v>-2.3315</v>
       </c>
       <c r="J479" s="5" t="inlineStr">
         <is>
@@ -21989,7 +22043,7 @@
         <v>0.0866</v>
       </c>
       <c r="I481" s="6" t="n">
-        <v>4.6322</v>
+        <v>-0.3022</v>
       </c>
       <c r="J481" s="5" t="inlineStr">
         <is>
@@ -22033,7 +22087,7 @@
         <v>-0.0775</v>
       </c>
       <c r="I482" s="3" t="n">
-        <v>-1.7935</v>
+        <v>-2.4711</v>
       </c>
       <c r="J482" s="2" t="inlineStr">
         <is>
@@ -22076,7 +22130,9 @@
       <c r="H483" s="6" t="n">
         <v>0.1577</v>
       </c>
-      <c r="I483" s="5" t="inlineStr"/>
+      <c r="I483" s="6" t="n">
+        <v>-0.3973</v>
+      </c>
       <c r="J483" s="5" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -22121,7 +22177,7 @@
         <v>0.1679</v>
       </c>
       <c r="I484" s="3" t="n">
-        <v>1.679</v>
+        <v>0.2955</v>
       </c>
       <c r="J484" s="2" t="inlineStr">
         <is>
@@ -22164,8 +22220,10 @@
       <c r="H485" s="6" t="n">
         <v>-0.1177</v>
       </c>
-      <c r="I485" s="6" t="n">
-        <v>-0.8070000000000001</v>
+      <c r="I485" s="5" t="inlineStr">
+        <is>
+          <t>-1.456.11</t>
+        </is>
       </c>
       <c r="J485" s="5" t="inlineStr">
         <is>
@@ -22211,7 +22269,7 @@
         <v>0.5293</v>
       </c>
       <c r="I486" s="3" t="n">
-        <v>0.9826</v>
+        <v>-0.4614</v>
       </c>
       <c r="J486" s="2" t="inlineStr">
         <is>
@@ -22259,7 +22317,7 @@
         <v>0.0048</v>
       </c>
       <c r="I487" s="6" t="n">
-        <v>-0.9414</v>
+        <v>-3.1045</v>
       </c>
       <c r="J487" s="5" t="inlineStr">
         <is>
@@ -22305,7 +22363,7 @@
         <v>0.018</v>
       </c>
       <c r="I488" s="3" t="n">
-        <v>0.9767</v>
+        <v>-0.6491</v>
       </c>
       <c r="J488" s="2" t="inlineStr">
         <is>
@@ -22351,7 +22409,7 @@
         <v>0.0118</v>
       </c>
       <c r="I489" s="6" t="n">
-        <v>-0.9026000000000001</v>
+        <v>-0.8634000000000001</v>
       </c>
       <c r="J489" s="5" t="inlineStr">
         <is>
@@ -22395,7 +22453,7 @@
         <v>0.4328</v>
       </c>
       <c r="I490" s="3" t="n">
-        <v>0.0198</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="J490" s="2" t="inlineStr">
         <is>
@@ -22439,7 +22497,7 @@
         <v>-0.1702</v>
       </c>
       <c r="I491" s="6" t="n">
-        <v>0.5165999999999999</v>
+        <v>-1.9167</v>
       </c>
       <c r="J491" s="5" t="inlineStr">
         <is>
@@ -22485,7 +22543,7 @@
         <v>0.3856</v>
       </c>
       <c r="I492" s="3" t="n">
-        <v>2.4774</v>
+        <v>0.1363</v>
       </c>
       <c r="J492" s="2" t="inlineStr">
         <is>
@@ -22529,7 +22587,7 @@
         <v>-1.1206</v>
       </c>
       <c r="I493" s="6" t="n">
-        <v>-0.8220999999999999</v>
+        <v>-7.040900000000001</v>
       </c>
       <c r="J493" s="5" t="inlineStr">
         <is>
@@ -22573,7 +22631,7 @@
         <v>-0.9031999999999999</v>
       </c>
       <c r="I494" s="3" t="n">
-        <v>0.0375</v>
+        <v>0.8837999999999999</v>
       </c>
       <c r="J494" s="2" t="inlineStr">
         <is>
@@ -22619,7 +22677,7 @@
         <v>0.5207999999999999</v>
       </c>
       <c r="I495" s="6" t="n">
-        <v>0.7056</v>
+        <v>-0.9906</v>
       </c>
       <c r="J495" s="5" t="inlineStr">
         <is>
@@ -22663,7 +22721,7 @@
         <v>-0.2463</v>
       </c>
       <c r="I496" s="3" t="n">
-        <v>-0.7854000000000001</v>
+        <v>0.0757</v>
       </c>
       <c r="J496" s="2" t="inlineStr">
         <is>
@@ -22706,7 +22764,9 @@
       <c r="H497" s="6" t="n">
         <v>0.0354</v>
       </c>
-      <c r="I497" s="5" t="inlineStr"/>
+      <c r="I497" s="6" t="n">
+        <v>0.7116</v>
+      </c>
       <c r="J497" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -22751,7 +22811,7 @@
         <v>0.1315</v>
       </c>
       <c r="I498" s="3" t="n">
-        <v>-0.3331</v>
+        <v>-0.4854</v>
       </c>
       <c r="J498" s="2" t="inlineStr">
         <is>
@@ -22796,7 +22856,9 @@
       <c r="H499" s="6" t="n">
         <v>0.2805</v>
       </c>
-      <c r="I499" s="5" t="inlineStr"/>
+      <c r="I499" s="6" t="n">
+        <v>0.4086</v>
+      </c>
       <c r="J499" s="5" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -22839,7 +22901,7 @@
         <v>-0.2375</v>
       </c>
       <c r="I500" s="3" t="n">
-        <v>-0.5550999999999999</v>
+        <v>-2.3984</v>
       </c>
       <c r="J500" s="2" t="inlineStr">
         <is>
@@ -22882,11 +22944,7 @@
       <c r="H501" s="6" t="n">
         <v>-0.2148</v>
       </c>
-      <c r="I501" s="5" t="inlineStr">
-        <is>
-          <t>-18.891.48</t>
-        </is>
-      </c>
+      <c r="I501" s="5" t="inlineStr"/>
       <c r="J501" s="5" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -22925,7 +22983,7 @@
         <v>-0.0097</v>
       </c>
       <c r="I502" s="3" t="n">
-        <v>0.8281999999999999</v>
+        <v>-3.335</v>
       </c>
       <c r="J502" s="2" t="inlineStr">
         <is>
@@ -22971,7 +23029,7 @@
         <v>0.1501</v>
       </c>
       <c r="I503" s="6" t="n">
-        <v>0.9762999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="J503" s="5" t="inlineStr">
         <is>
@@ -23017,7 +23075,7 @@
         <v>0.2763</v>
       </c>
       <c r="I504" s="3" t="n">
-        <v>0.537</v>
+        <v>0.0601</v>
       </c>
       <c r="J504" s="2" t="inlineStr">
         <is>
@@ -23061,7 +23119,7 @@
         <v>-1.4367</v>
       </c>
       <c r="I505" s="6" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-3.178</v>
       </c>
       <c r="J505" s="5" t="inlineStr">
         <is>
@@ -23104,9 +23162,7 @@
       <c r="H506" s="3" t="n">
         <v>-1.089</v>
       </c>
-      <c r="I506" s="3" t="n">
-        <v>0.5474</v>
-      </c>
+      <c r="I506" s="2" t="inlineStr"/>
       <c r="J506" s="2" t="inlineStr">
         <is>
           <t>Perakende satış</t>
@@ -23146,7 +23202,9 @@
         <v>0.06269999999999999</v>
       </c>
       <c r="H507" s="5" t="inlineStr"/>
-      <c r="I507" s="5" t="inlineStr"/>
+      <c r="I507" s="6" t="n">
+        <v>-0.9567</v>
+      </c>
       <c r="J507" s="5" t="inlineStr">
         <is>
           <t>Elektronik teknoloji</t>
@@ -23190,9 +23248,7 @@
       <c r="H508" s="3" t="n">
         <v>0.0366</v>
       </c>
-      <c r="I508" s="3" t="n">
-        <v>-0.3546</v>
-      </c>
+      <c r="I508" s="2" t="inlineStr"/>
       <c r="J508" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -23236,9 +23292,7 @@
       <c r="H509" s="6" t="n">
         <v>0.2997</v>
       </c>
-      <c r="I509" s="6" t="n">
-        <v>3.322</v>
-      </c>
+      <c r="I509" s="5" t="inlineStr"/>
       <c r="J509" s="5" t="inlineStr">
         <is>
           <t>Dayanıklı tüketim malları</t>
@@ -23282,7 +23336,7 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>-4.092.45</t>
+          <t>-1.256.99</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
@@ -23327,7 +23381,7 @@
         <v>-0.1167</v>
       </c>
       <c r="I511" s="6" t="n">
-        <v>-3.1244</v>
+        <v>0.0278</v>
       </c>
       <c r="J511" s="5" t="inlineStr">
         <is>
@@ -23371,7 +23425,7 @@
         <v>-0.2944</v>
       </c>
       <c r="I512" s="3" t="n">
-        <v>-1.0668</v>
+        <v>-0.6470999999999999</v>
       </c>
       <c r="J512" s="2" t="inlineStr">
         <is>
@@ -23416,7 +23470,11 @@
       <c r="H513" s="6" t="n">
         <v>0.077</v>
       </c>
-      <c r="I513" s="5" t="inlineStr"/>
+      <c r="I513" s="5" t="inlineStr">
+        <is>
+          <t>+54.693.97</t>
+        </is>
+      </c>
       <c r="J513" s="5" t="inlineStr">
         <is>
           <t>Dağıtım servisleri</t>
@@ -23459,7 +23517,7 @@
         <v>-0.3331</v>
       </c>
       <c r="I514" s="3" t="n">
-        <v>-3.1176</v>
+        <v>-0.6662</v>
       </c>
       <c r="J514" s="2" t="inlineStr">
         <is>
@@ -23503,7 +23561,7 @@
         <v>-0.1254</v>
       </c>
       <c r="I515" s="6" t="n">
-        <v>-6.167000000000001</v>
+        <v>-7.7801</v>
       </c>
       <c r="J515" s="5" t="inlineStr">
         <is>
@@ -23546,10 +23604,8 @@
       <c r="H516" s="3" t="n">
         <v>-0.555</v>
       </c>
-      <c r="I516" s="2" t="inlineStr">
-        <is>
-          <t>-1.390.39</t>
-        </is>
+      <c r="I516" s="3" t="n">
+        <v>-6.502000000000001</v>
       </c>
       <c r="J516" s="2" t="inlineStr">
         <is>
@@ -23593,7 +23649,7 @@
         <v>-0.07200000000000001</v>
       </c>
       <c r="I517" s="6" t="n">
-        <v>-1.7171</v>
+        <v>-5.0791</v>
       </c>
       <c r="J517" s="5" t="inlineStr">
         <is>
@@ -23637,7 +23693,7 @@
         <v>-0.6823</v>
       </c>
       <c r="I518" s="3" t="n">
-        <v>-0.9802</v>
+        <v>-2.0132</v>
       </c>
       <c r="J518" s="2" t="inlineStr">
         <is>
@@ -23682,7 +23738,9 @@
       <c r="H519" s="6" t="n">
         <v>0.05309999999999999</v>
       </c>
-      <c r="I519" s="5" t="inlineStr"/>
+      <c r="I519" s="6" t="n">
+        <v>1.1582</v>
+      </c>
       <c r="J519" s="5" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -23727,7 +23785,7 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I520" s="3" t="n">
-        <v>-0.3175</v>
+        <v>0.2585</v>
       </c>
       <c r="J520" s="2" t="inlineStr">
         <is>
@@ -23771,7 +23829,7 @@
         <v>-1.4376</v>
       </c>
       <c r="I521" s="6" t="n">
-        <v>0.5175</v>
+        <v>-5.4758</v>
       </c>
       <c r="J521" s="5" t="inlineStr">
         <is>
@@ -23816,10 +23874,8 @@
       <c r="H522" s="3" t="n">
         <v>2.2403</v>
       </c>
-      <c r="I522" s="2" t="inlineStr">
-        <is>
-          <t>+8.244.52</t>
-        </is>
+      <c r="I522" s="3" t="n">
+        <v>-0.7998000000000001</v>
       </c>
       <c r="J522" s="2" t="inlineStr">
         <is>
@@ -23862,7 +23918,9 @@
       <c r="H523" s="6" t="n">
         <v>0.3692</v>
       </c>
-      <c r="I523" s="5" t="inlineStr"/>
+      <c r="I523" s="6" t="n">
+        <v>0.507</v>
+      </c>
       <c r="J523" s="5" t="inlineStr">
         <is>
           <t>Teknoloji hizmetleri</t>
@@ -23904,7 +23962,7 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>-6.908.05</t>
+          <t>-1.287.47</t>
         </is>
       </c>
       <c r="J524" s="2" t="inlineStr">
@@ -23951,7 +24009,7 @@
         <v>0.316</v>
       </c>
       <c r="I525" s="6" t="n">
-        <v>0.0356</v>
+        <v>0.8517</v>
       </c>
       <c r="J525" s="5" t="inlineStr">
         <is>
@@ -23994,8 +24052,10 @@
       <c r="H526" s="3" t="n">
         <v>-0.0173</v>
       </c>
-      <c r="I526" s="3" t="n">
-        <v>0.7707999999999999</v>
+      <c r="I526" s="2" t="inlineStr">
+        <is>
+          <t>-5.907.48</t>
+        </is>
       </c>
       <c r="J526" s="2" t="inlineStr">
         <is>
@@ -24038,7 +24098,9 @@
       <c r="H527" s="6" t="n">
         <v>0.2045</v>
       </c>
-      <c r="I527" s="5" t="inlineStr"/>
+      <c r="I527" s="6" t="n">
+        <v>7.1809</v>
+      </c>
       <c r="J527" s="5" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -24081,7 +24143,7 @@
         <v>-0.1812</v>
       </c>
       <c r="I528" s="3" t="n">
-        <v>-0.1451</v>
+        <v>0.1259</v>
       </c>
       <c r="J528" s="2" t="inlineStr">
         <is>
@@ -24126,10 +24188,8 @@
       <c r="H529" s="6" t="n">
         <v>0.0607</v>
       </c>
-      <c r="I529" s="5" t="inlineStr">
-        <is>
-          <t>+2.644.01</t>
-        </is>
+      <c r="I529" s="6" t="n">
+        <v>-0.9726</v>
       </c>
       <c r="J529" s="5" t="inlineStr">
         <is>
@@ -24175,7 +24235,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I530" s="3" t="n">
-        <v>-0.2903</v>
+        <v>-0.3923</v>
       </c>
       <c r="J530" s="2" t="inlineStr">
         <is>
@@ -24220,7 +24280,7 @@
       </c>
       <c r="I531" s="5" t="inlineStr">
         <is>
-          <t>-2.059.11</t>
+          <t>-10.584.16</t>
         </is>
       </c>
       <c r="J531" s="5" t="inlineStr">
@@ -24264,9 +24324,7 @@
       <c r="H532" s="3" t="n">
         <v>0.794</v>
       </c>
-      <c r="I532" s="3" t="n">
-        <v>1.092</v>
-      </c>
+      <c r="I532" s="2" t="inlineStr"/>
       <c r="J532" s="2" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -24311,7 +24369,7 @@
         <v>0.3276</v>
       </c>
       <c r="I533" s="6" t="n">
-        <v>0.3218</v>
+        <v>0.1497</v>
       </c>
       <c r="J533" s="5" t="inlineStr">
         <is>
@@ -24351,7 +24409,7 @@
         <v>-0.2799</v>
       </c>
       <c r="I534" s="3" t="n">
-        <v>0.6353</v>
+        <v>0.9349</v>
       </c>
       <c r="J534" s="2" t="inlineStr">
         <is>
@@ -24394,10 +24452,8 @@
       <c r="H535" s="6" t="n">
         <v>-0.3587</v>
       </c>
-      <c r="I535" s="5" t="inlineStr">
-        <is>
-          <t>-23.881.74</t>
-        </is>
+      <c r="I535" s="6" t="n">
+        <v>-9.0931</v>
       </c>
       <c r="J535" s="5" t="inlineStr">
         <is>
@@ -24441,7 +24497,7 @@
         <v>-0.0732</v>
       </c>
       <c r="I536" s="3" t="n">
-        <v>-2.695</v>
+        <v>-0.586</v>
       </c>
       <c r="J536" s="2" t="inlineStr">
         <is>
@@ -24484,7 +24540,9 @@
       <c r="H537" s="6" t="n">
         <v>-0.2169</v>
       </c>
-      <c r="I537" s="5" t="inlineStr"/>
+      <c r="I537" s="6" t="n">
+        <v>-0.7524</v>
+      </c>
       <c r="J537" s="5" t="inlineStr">
         <is>
           <t>Ticari hizmetler</t>
@@ -24527,7 +24585,7 @@
         <v>-0.0331</v>
       </c>
       <c r="I538" s="3" t="n">
-        <v>0.4891</v>
+        <v>-0.1747</v>
       </c>
       <c r="J538" s="2" t="inlineStr">
         <is>
@@ -24617,7 +24675,7 @@
         <v>0.2238</v>
       </c>
       <c r="I540" s="3" t="n">
-        <v>1.3322</v>
+        <v>0.1902</v>
       </c>
       <c r="J540" s="2" t="inlineStr">
         <is>
@@ -24663,7 +24721,7 @@
         <v>0.4916</v>
       </c>
       <c r="I541" s="6" t="n">
-        <v>0.8411</v>
+        <v>2.6125</v>
       </c>
       <c r="J541" s="5" t="inlineStr">
         <is>
@@ -24709,7 +24767,7 @@
         <v>0.0381</v>
       </c>
       <c r="I542" s="3" t="n">
-        <v>2.8654</v>
+        <v>-1.5645</v>
       </c>
       <c r="J542" s="2" t="inlineStr">
         <is>
@@ -24752,8 +24810,10 @@
       <c r="H543" s="6" t="n">
         <v>-0.1301</v>
       </c>
-      <c r="I543" s="6" t="n">
-        <v>-0.8764</v>
+      <c r="I543" s="5" t="inlineStr">
+        <is>
+          <t>-2.832.44</t>
+        </is>
       </c>
       <c r="J543" s="5" t="inlineStr">
         <is>
@@ -24796,8 +24856,10 @@
       <c r="H544" s="3" t="n">
         <v>-0.0555</v>
       </c>
-      <c r="I544" s="3" t="n">
-        <v>-1.3604</v>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>-1.082.24</t>
+        </is>
       </c>
       <c r="J544" s="2" t="inlineStr">
         <is>
@@ -24840,8 +24902,10 @@
       <c r="H545" s="6" t="n">
         <v>-0.1361</v>
       </c>
-      <c r="I545" s="6" t="n">
-        <v>-2.4665</v>
+      <c r="I545" s="5" t="inlineStr">
+        <is>
+          <t>-1.196.36</t>
+        </is>
       </c>
       <c r="J545" s="5" t="inlineStr">
         <is>
@@ -24887,7 +24951,7 @@
         <v>0.3294</v>
       </c>
       <c r="I546" s="3" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.1253</v>
       </c>
       <c r="J546" s="2" t="inlineStr">
         <is>
@@ -24927,7 +24991,7 @@
         <v>-0.5649000000000001</v>
       </c>
       <c r="I547" s="6" t="n">
-        <v>-2.5247</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="J547" s="5" t="inlineStr">
         <is>
@@ -24973,7 +25037,7 @@
         <v>0.004699999999999999</v>
       </c>
       <c r="I548" s="3" t="n">
-        <v>-0.8634999999999999</v>
+        <v>-2.1441</v>
       </c>
       <c r="J548" s="2" t="inlineStr">
         <is>
@@ -25019,7 +25083,7 @@
         <v>1.1992</v>
       </c>
       <c r="I549" s="6" t="n">
-        <v>2.9912</v>
+        <v>0.3524</v>
       </c>
       <c r="J549" s="5" t="inlineStr">
         <is>
@@ -25064,7 +25128,9 @@
       <c r="H550" s="3" t="n">
         <v>0.1448</v>
       </c>
-      <c r="I550" s="2" t="inlineStr"/>
+      <c r="I550" s="3" t="n">
+        <v>0.4836</v>
+      </c>
       <c r="J550" s="2" t="inlineStr">
         <is>
           <t>Sağlık teknolojisi</t>
@@ -25106,8 +25172,10 @@
       <c r="H551" s="6" t="n">
         <v>-0.0564</v>
       </c>
-      <c r="I551" s="6" t="n">
-        <v>-8.648400000000001</v>
+      <c r="I551" s="5" t="inlineStr">
+        <is>
+          <t>-679.051.01</t>
+        </is>
       </c>
       <c r="J551" s="5" t="inlineStr">
         <is>
@@ -25152,9 +25220,7 @@
       <c r="H552" s="3" t="n">
         <v>0.1129</v>
       </c>
-      <c r="I552" s="3" t="n">
-        <v>0.1754</v>
-      </c>
+      <c r="I552" s="2" t="inlineStr"/>
       <c r="J552" s="2" t="inlineStr">
         <is>
           <t>Tüketici hizmetleri</t>
@@ -25191,7 +25257,7 @@
         <v>-0.3366</v>
       </c>
       <c r="I553" s="6" t="n">
-        <v>-0.2179</v>
+        <v>0.5811999999999999</v>
       </c>
       <c r="J553" s="5" t="inlineStr">
         <is>
@@ -25235,7 +25301,7 @@
         <v>-0.3087</v>
       </c>
       <c r="I554" s="3" t="n">
-        <v>-1.7311</v>
+        <v>0.4908</v>
       </c>
       <c r="J554" s="2" t="inlineStr">
         <is>
@@ -25281,7 +25347,7 @@
         </is>
       </c>
       <c r="I555" s="6" t="n">
-        <v>-1.0669</v>
+        <v>-0.7162999999999999</v>
       </c>
       <c r="J555" s="5" t="inlineStr">
         <is>
@@ -25325,7 +25391,7 @@
         <v>-0.0998</v>
       </c>
       <c r="I556" s="3" t="n">
-        <v>0.1901</v>
+        <v>-4.3494</v>
       </c>
       <c r="J556" s="2" t="inlineStr">
         <is>
@@ -25364,10 +25430,8 @@
       <c r="H557" s="6" t="n">
         <v>-0.7977</v>
       </c>
-      <c r="I557" s="5" t="inlineStr">
-        <is>
-          <t>-1.086.00</t>
-        </is>
+      <c r="I557" s="6" t="n">
+        <v>-4.018899999999999</v>
       </c>
       <c r="J557" s="5" t="inlineStr">
         <is>
@@ -25411,7 +25475,7 @@
         <v>-0.1124</v>
       </c>
       <c r="I558" s="3" t="n">
-        <v>-1.6323</v>
+        <v>-1.529</v>
       </c>
       <c r="J558" s="2" t="inlineStr">
         <is>
@@ -25455,7 +25519,7 @@
         <v>-0.2916</v>
       </c>
       <c r="I559" s="6" t="n">
-        <v>-0.0796</v>
+        <v>-0.6609</v>
       </c>
       <c r="J559" s="5" t="inlineStr">
         <is>
@@ -25498,9 +25562,7 @@
       <c r="H560" s="3" t="n">
         <v>-0.1302</v>
       </c>
-      <c r="I560" s="3" t="n">
-        <v>-3.7307</v>
-      </c>
+      <c r="I560" s="2" t="inlineStr"/>
       <c r="J560" s="2" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -25544,8 +25606,10 @@
       <c r="H561" s="6" t="n">
         <v>0.4103</v>
       </c>
-      <c r="I561" s="6" t="n">
-        <v>4.5861</v>
+      <c r="I561" s="5" t="inlineStr">
+        <is>
+          <t>+3.055.21</t>
+        </is>
       </c>
       <c r="J561" s="5" t="inlineStr">
         <is>
@@ -25591,7 +25655,7 @@
         <v>0.2511</v>
       </c>
       <c r="I562" s="3" t="n">
-        <v>0.1833</v>
+        <v>-0.2499</v>
       </c>
       <c r="J562" s="2" t="inlineStr">
         <is>
@@ -25677,7 +25741,7 @@
         <v>-0.1359</v>
       </c>
       <c r="I564" s="3" t="n">
-        <v>-4.048999999999999</v>
+        <v>-0.6534</v>
       </c>
       <c r="J564" s="2" t="inlineStr">
         <is>
@@ -25720,9 +25784,7 @@
       <c r="H565" s="6" t="n">
         <v>-0.2336</v>
       </c>
-      <c r="I565" s="6" t="n">
-        <v>0.1405</v>
-      </c>
+      <c r="I565" s="5" t="inlineStr"/>
       <c r="J565" s="5" t="inlineStr">
         <is>
           <t>Ticari hizmetler</t>
@@ -25766,7 +25828,9 @@
       <c r="H566" s="3" t="n">
         <v>0.3759</v>
       </c>
-      <c r="I566" s="2" t="inlineStr"/>
+      <c r="I566" s="3" t="n">
+        <v>0.9841</v>
+      </c>
       <c r="J566" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -25810,9 +25874,7 @@
       <c r="H567" s="6" t="n">
         <v>0.2047</v>
       </c>
-      <c r="I567" s="6" t="n">
-        <v>0.4454</v>
-      </c>
+      <c r="I567" s="5" t="inlineStr"/>
       <c r="J567" s="5" t="inlineStr">
         <is>
           <t>Teknoloji hizmetleri</t>
@@ -25856,7 +25918,9 @@
       <c r="H568" s="3" t="n">
         <v>0.2784</v>
       </c>
-      <c r="I568" s="2" t="inlineStr"/>
+      <c r="I568" s="3" t="n">
+        <v>-1.188</v>
+      </c>
       <c r="J568" s="2" t="inlineStr">
         <is>
           <t>Ticari hizmetler</t>
@@ -25894,9 +25958,7 @@
       <c r="H569" s="6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="I569" s="6" t="n">
-        <v>-1.4448</v>
-      </c>
+      <c r="I569" s="5" t="inlineStr"/>
       <c r="J569" s="5" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -25934,7 +25996,9 @@
       <c r="H570" s="3" t="n">
         <v>0.4482</v>
       </c>
-      <c r="I570" s="2" t="inlineStr"/>
+      <c r="I570" s="3" t="n">
+        <v>0.09619999999999999</v>
+      </c>
       <c r="J570" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -25977,7 +26041,7 @@
         <v>-0.6681</v>
       </c>
       <c r="I571" s="6" t="n">
-        <v>-0.3978</v>
+        <v>-0.3896</v>
       </c>
       <c r="J571" s="5" t="inlineStr">
         <is>
@@ -26019,7 +26083,7 @@
         <v>-0.1117</v>
       </c>
       <c r="I572" s="3" t="n">
-        <v>-0.735</v>
+        <v>-5.8214</v>
       </c>
       <c r="J572" s="2" t="inlineStr">
         <is>
@@ -26063,7 +26127,7 @@
         <v>-0.4695</v>
       </c>
       <c r="I573" s="6" t="n">
-        <v>-2.3112</v>
+        <v>0.4335</v>
       </c>
       <c r="J573" s="5" t="inlineStr">
         <is>
@@ -26109,7 +26173,7 @@
         <v>0.1167</v>
       </c>
       <c r="I574" s="3" t="n">
-        <v>0.1046</v>
+        <v>-0.9891</v>
       </c>
       <c r="J574" s="2" t="inlineStr">
         <is>
@@ -26155,7 +26219,7 @@
         <v>0.1819</v>
       </c>
       <c r="I575" s="6" t="n">
-        <v>0.4905</v>
+        <v>0.6855</v>
       </c>
       <c r="J575" s="5" t="inlineStr">
         <is>
@@ -26199,7 +26263,7 @@
         <v>-0.9847</v>
       </c>
       <c r="I576" s="3" t="n">
-        <v>0.6998000000000001</v>
+        <v>-2.8801</v>
       </c>
       <c r="J576" s="2" t="inlineStr">
         <is>
@@ -26242,10 +26306,8 @@
       <c r="H577" s="6" t="n">
         <v>0.8465</v>
       </c>
-      <c r="I577" s="5" t="inlineStr">
-        <is>
-          <t>+6.400.34</t>
-        </is>
+      <c r="I577" s="6" t="n">
+        <v>-0.7746999999999999</v>
       </c>
       <c r="J577" s="5" t="inlineStr">
         <is>
@@ -26295,7 +26357,7 @@
         <v>0.1819</v>
       </c>
       <c r="I578" s="3" t="n">
-        <v>0.4905</v>
+        <v>0.6855</v>
       </c>
       <c r="J578" s="2" t="inlineStr">
         <is>
@@ -26308,54 +26370,66 @@
     <row r="579">
       <c r="A579" s="5" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B579" s="5" t="inlineStr">
         <is>
-          <t>82,76</t>
+          <t>123,1</t>
         </is>
       </c>
       <c r="C579" s="6" t="n">
-        <v>-0.0059</v>
+        <v>0.0008</v>
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>18,83M</t>
+          <t>356,41B</t>
         </is>
       </c>
       <c r="E579" s="7" t="n">
-        <v>43.97</v>
+        <v>48.58</v>
       </c>
       <c r="F579" s="5" t="inlineStr"/>
       <c r="G579" s="5" t="inlineStr"/>
-      <c r="H579" s="5" t="inlineStr"/>
-      <c r="I579" s="5" t="inlineStr"/>
-      <c r="J579" s="5" t="inlineStr"/>
-      <c r="K579" s="5" t="inlineStr"/>
+      <c r="H579" s="6" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="I579" s="6" t="n">
+        <v>-0.4897</v>
+      </c>
+      <c r="J579" s="5" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
+      <c r="K579" s="5" t="inlineStr">
+        <is>
+          <t>BIST TUM-100. BIST TÜM. BIST TİCARET. BIST HİZMETLER. BIST ANA</t>
+        </is>
+      </c>
       <c r="L579" s="5" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B580" s="2" t="inlineStr">
         <is>
-          <t>35,82</t>
+          <t>27,12</t>
         </is>
       </c>
       <c r="C580" s="3" t="n">
-        <v>-0.017</v>
+        <v>0.0015</v>
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>4,91M</t>
+          <t>17,10M</t>
         </is>
       </c>
       <c r="E580" s="4" t="n">
-        <v>46.44</v>
+        <v>52.08</v>
       </c>
       <c r="F580" s="2" t="inlineStr"/>
       <c r="G580" s="2" t="inlineStr"/>
@@ -26363,12 +26437,12 @@
       <c r="I580" s="2" t="inlineStr"/>
       <c r="J580" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="K580" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST SINAI. BIST TÜM. BIST TAŞ TOPRAK. BIST HALKA ARZ. BIST ANA. BIST MANİSA</t>
+          <t>BIST TUM-100. BIST TÜM. BIST İNŞAAT. BIST HALKA ARZ. BIST HİZMETLER. BIST İSTANBUL. BIST KATILIM TÜM. BIST ANA</t>
         </is>
       </c>
       <c r="L580" s="2" t="inlineStr"/>
@@ -26376,24 +26450,24 @@
     <row r="581">
       <c r="A581" s="5" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="B581" s="5" t="inlineStr">
         <is>
-          <t>27,10</t>
+          <t>12,03</t>
         </is>
       </c>
       <c r="C581" s="6" t="n">
-        <v>-0.0266</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D581" s="5" t="inlineStr">
         <is>
-          <t>21,12M</t>
+          <t>120,51M</t>
         </is>
       </c>
       <c r="E581" s="7" t="n">
-        <v>54.93</v>
+        <v>83.16</v>
       </c>
       <c r="F581" s="5" t="inlineStr"/>
       <c r="G581" s="5" t="inlineStr"/>
@@ -26439,7 +26513,7 @@
         <v>-9.409700000000001</v>
       </c>
       <c r="I582" s="3" t="n">
-        <v>-3.7502</v>
+        <v>-4.155</v>
       </c>
       <c r="J582" s="2" t="inlineStr">
         <is>
@@ -26452,24 +26526,24 @@
     <row r="583">
       <c r="A583" s="5" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B583" s="5" t="inlineStr">
         <is>
-          <t>244,0</t>
+          <t>13,36</t>
         </is>
       </c>
       <c r="C583" s="6" t="n">
-        <v>0.0243</v>
+        <v>-0.0052</v>
       </c>
       <c r="D583" s="5" t="inlineStr">
         <is>
-          <t>8,92B</t>
+          <t>71,20M</t>
         </is>
       </c>
       <c r="E583" s="7" t="n">
-        <v>37.83</v>
+        <v>54.58</v>
       </c>
       <c r="F583" s="5" t="inlineStr"/>
       <c r="G583" s="5" t="inlineStr"/>
@@ -26480,81 +26554,89 @@
           <t>İşlenebilen endüstriler</t>
         </is>
       </c>
-      <c r="K583" s="5" t="inlineStr"/>
+      <c r="K583" s="5" t="inlineStr">
+        <is>
+          <t>BIST TUM-100. BIST SINAI. BIST TÜM. BIST KİMYA PETROL PLASTİK. BIST HALKA ARZ. BIST KATILIM TÜM. BIST ANA. BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="L583" s="5" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B584" s="2" t="inlineStr">
         <is>
-          <t>60,50</t>
+          <t>8,53</t>
         </is>
       </c>
       <c r="C584" s="3" t="n">
-        <v>-0.0194</v>
+        <v>-0.0469</v>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>3,13M</t>
+          <t>199,28B</t>
         </is>
       </c>
       <c r="E584" s="4" t="n">
-        <v>47.59</v>
+        <v>45.93</v>
       </c>
       <c r="F584" s="2" t="inlineStr"/>
       <c r="G584" s="2" t="inlineStr"/>
-      <c r="H584" s="2" t="inlineStr"/>
-      <c r="I584" s="2" t="inlineStr"/>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>-2.362.91</t>
+        </is>
+      </c>
+      <c r="I584" s="3" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="J584" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="K584" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100. BIST TÜM. BIST HALKA ARZ. BIST MALİ. BIST ANA. BIST TEMETTU</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="K584" s="2" t="inlineStr"/>
       <c r="L584" s="2" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="5" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B585" s="5" t="inlineStr">
         <is>
-          <t>44,58</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="C585" s="6" t="n">
-        <v>0.0059</v>
+        <v>0.0152</v>
       </c>
       <c r="D585" s="5" t="inlineStr">
         <is>
-          <t>30,63M</t>
+          <t>95,55M</t>
         </is>
       </c>
       <c r="E585" s="7" t="n">
-        <v>62.46</v>
+        <v>41.64</v>
       </c>
       <c r="F585" s="5" t="inlineStr"/>
       <c r="G585" s="5" t="inlineStr"/>
       <c r="H585" s="5" t="inlineStr"/>
-      <c r="I585" s="5" t="inlineStr"/>
+      <c r="I585" s="6" t="n">
+        <v>-2.0083</v>
+      </c>
       <c r="J585" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="K585" s="5" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST TEKNOLOJİ. BIST BILISIM. BIST HALKA ARZ. BIST İSTANBUL. BIST KATILIM TÜM. BIST ANA. BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST 100. BIST 100 AĞIRLIK SINIRLAMALI 10. BIST TÜM. BIST SPOR. BIST HİZMETLER. BIST İSTANBUL. BIST 100-30. BIST 100 AĞIRLIK SINIRLAMALI 25. BIST YILDIZ</t>
         </is>
       </c>
       <c r="L585" s="5" t="inlineStr"/>
@@ -26562,24 +26644,24 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="B586" s="2" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>27,10</t>
         </is>
       </c>
       <c r="C586" s="3" t="n">
-        <v>-0.0052</v>
+        <v>-0.0266</v>
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>71,20M</t>
+          <t>21,12M</t>
         </is>
       </c>
       <c r="E586" s="4" t="n">
-        <v>54.58</v>
+        <v>54.93</v>
       </c>
       <c r="F586" s="2" t="inlineStr"/>
       <c r="G586" s="2" t="inlineStr"/>
@@ -26587,12 +26669,12 @@
       <c r="I586" s="2" t="inlineStr"/>
       <c r="J586" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST SINAI. BIST TÜM. BIST KİMYA PETROL PLASTİK. BIST HALKA ARZ. BIST KATILIM TÜM. BIST ANA. BIST KOCAELI</t>
+          <t>BIST TUM-100. BIST TÜM. BIST GAYRİMENKUL YO. BIST HALKA ARZ. BIST MALİ. BIST ANA</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr"/>
@@ -26600,24 +26682,24 @@
     <row r="587">
       <c r="A587" s="5" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B587" s="5" t="inlineStr">
         <is>
-          <t>23,70</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="C587" s="6" t="n">
-        <v>0.0505</v>
+        <v>-0.0017</v>
       </c>
       <c r="D587" s="5" t="inlineStr">
         <is>
-          <t>18,74M</t>
+          <t>10,00M</t>
         </is>
       </c>
       <c r="E587" s="7" t="n">
-        <v>55.2</v>
+        <v>48.59</v>
       </c>
       <c r="F587" s="5" t="inlineStr"/>
       <c r="G587" s="5" t="inlineStr"/>
@@ -26625,37 +26707,33 @@
       <c r="I587" s="5" t="inlineStr"/>
       <c r="J587" s="5" t="inlineStr">
         <is>
-          <t>Elektrik. Su. Gaz Hizmetleri</t>
-        </is>
-      </c>
-      <c r="K587" s="5" t="inlineStr">
-        <is>
-          <t>BIST ELEKTRIK. BIST TUM-100. BIST TÜM. BIST HALKA ARZ. BIST HİZMETLER. BIST İSTANBUL. BIST KATILIM TÜM. BIST ANA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="K587" s="5" t="inlineStr"/>
       <c r="L587" s="5" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B588" s="2" t="inlineStr">
         <is>
-          <t>15,82</t>
+          <t>44,58</t>
         </is>
       </c>
       <c r="C588" s="3" t="n">
-        <v>-0.0561</v>
+        <v>0.0059</v>
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>92,49M</t>
+          <t>30,63M</t>
         </is>
       </c>
       <c r="E588" s="4" t="n">
-        <v>55.41</v>
+        <v>62.46</v>
       </c>
       <c r="F588" s="2" t="inlineStr"/>
       <c r="G588" s="2" t="inlineStr"/>
@@ -26663,12 +26741,12 @@
       <c r="I588" s="2" t="inlineStr"/>
       <c r="J588" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST GAYRİMENKUL YO. BIST HALKA ARZ. BIST MALİ. BIST KATILIM TÜM. BIST ANA</t>
+          <t>BIST TUM-100. BIST TÜM. BIST TEKNOLOJİ. BIST BILISIM. BIST HALKA ARZ. BIST İSTANBUL. BIST KATILIM TÜM. BIST ANA. BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr"/>
@@ -26676,77 +26754,79 @@
     <row r="589">
       <c r="A589" s="5" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B589" s="5" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="C589" s="6" t="n">
-        <v>-0.0469</v>
+        <v>-0.0551</v>
       </c>
       <c r="D589" s="5" t="inlineStr">
         <is>
-          <t>199,28B</t>
+          <t>44,45M</t>
         </is>
       </c>
       <c r="E589" s="7" t="n">
-        <v>45.93</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="F589" s="5" t="inlineStr"/>
       <c r="G589" s="5" t="inlineStr"/>
-      <c r="H589" s="5" t="inlineStr">
-        <is>
-          <t>-2.362.91</t>
-        </is>
-      </c>
-      <c r="I589" s="6" t="n">
-        <v>-1.4696</v>
-      </c>
+      <c r="H589" s="5" t="inlineStr"/>
+      <c r="I589" s="5" t="inlineStr"/>
       <c r="J589" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="K589" s="5" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="K589" s="5" t="inlineStr">
+        <is>
+          <t>BIST TUM-100. BIST TÜM. BIST HOLDING VE YATIRIM. BIST MALİ. BIST ANA</t>
+        </is>
+      </c>
       <c r="L589" s="5" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B590" s="2" t="inlineStr">
         <is>
-          <t>149,6</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="C590" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>15,49M</t>
+          <t>15,36M</t>
         </is>
       </c>
       <c r="E590" s="4" t="n">
-        <v>74.16</v>
+        <v>60.82</v>
       </c>
       <c r="F590" s="2" t="inlineStr"/>
       <c r="G590" s="2" t="inlineStr"/>
-      <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="2" t="inlineStr"/>
+      <c r="H590" s="3" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="I590" s="3" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="J590" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST TEKNOLOJİ. BIST BILISIM. BIST HALKA ARZ. BIST İSTANBUL. BIST KATILIM TÜM. BIST ANA. BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100. BIST TÜM. BIST HİZMETLER. BIST İSTANBUL. BIST YILDIZ</t>
         </is>
       </c>
       <c r="L590" s="2" t="inlineStr"/>
@@ -26754,43 +26834,37 @@
     <row r="591">
       <c r="A591" s="5" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B591" s="5" t="inlineStr">
         <is>
-          <t>17,30</t>
+          <t>149,6</t>
         </is>
       </c>
       <c r="C591" s="6" t="n">
-        <v>-0.0035</v>
+        <v>0.1</v>
       </c>
       <c r="D591" s="5" t="inlineStr">
         <is>
-          <t>11,97M</t>
+          <t>15,49M</t>
         </is>
       </c>
       <c r="E591" s="7" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="F591" s="6" t="n">
-        <v>1.6352</v>
-      </c>
+        <v>74.16</v>
+      </c>
+      <c r="F591" s="5" t="inlineStr"/>
       <c r="G591" s="5" t="inlineStr"/>
-      <c r="H591" s="6" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="I591" s="6" t="n">
-        <v>-0.8891</v>
-      </c>
+      <c r="H591" s="5" t="inlineStr"/>
+      <c r="I591" s="5" t="inlineStr"/>
       <c r="J591" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="K591" s="5" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST HOLDING VE YATIRIM. BIST MALİ. BIST KATILIM 100. BIST KATILIM TÜM. BIST YILDIZ. BIST KATILIM 50. BIST KONYA</t>
+          <t>BIST TUM-100. BIST TÜM. BIST TEKNOLOJİ. BIST BILISIM. BIST HALKA ARZ. BIST İSTANBUL. BIST KATILIM TÜM. BIST ANA. BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="L591" s="5" t="inlineStr"/>
@@ -26798,85 +26872,67 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B592" s="2" t="inlineStr">
         <is>
-          <t>8,15</t>
+          <t>82,76</t>
         </is>
       </c>
       <c r="C592" s="3" t="n">
-        <v>-0.09939999999999999</v>
+        <v>-0.0059</v>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>98,26M</t>
+          <t>18,83M</t>
         </is>
       </c>
       <c r="E592" s="4" t="n">
-        <v>17.32</v>
+        <v>43.97</v>
       </c>
       <c r="F592" s="2" t="inlineStr"/>
       <c r="G592" s="2" t="inlineStr"/>
-      <c r="H592" s="3" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
-      <c r="I592" s="3" t="n">
-        <v>-1.0057</v>
-      </c>
-      <c r="J592" s="2" t="inlineStr">
-        <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
-        </is>
-      </c>
-      <c r="K592" s="2" t="inlineStr">
-        <is>
-          <t>BIST 100. BIST 100 AĞIRLIK SINIRLAMALI 10. BIST GIDA ICECEK. BIST SINAI. BIST TÜM. BIST HALKA ARZ. BIST 100-30. BIST KATILIM 100. BIST KATILIM TÜM. BIST 100 AĞIRLIK SINIRLAMALI 25. BIST YILDIZ. BIST KATILIM 50</t>
-        </is>
-      </c>
+      <c r="H592" s="2" t="inlineStr"/>
+      <c r="I592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
+      <c r="K592" s="2" t="inlineStr"/>
       <c r="L592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="5" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B593" s="5" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>35,82</t>
         </is>
       </c>
       <c r="C593" s="6" t="n">
-        <v>0.0803</v>
+        <v>-0.017</v>
       </c>
       <c r="D593" s="5" t="inlineStr">
         <is>
-          <t>38,53M</t>
+          <t>4,91M</t>
         </is>
       </c>
       <c r="E593" s="7" t="n">
-        <v>61.31</v>
+        <v>46.44</v>
       </c>
       <c r="F593" s="5" t="inlineStr"/>
       <c r="G593" s="5" t="inlineStr"/>
-      <c r="H593" s="5" t="inlineStr">
-        <is>
-          <t>-19.163.42</t>
-        </is>
-      </c>
-      <c r="I593" s="6" t="n">
-        <v>-1.3821</v>
-      </c>
+      <c r="H593" s="5" t="inlineStr"/>
+      <c r="I593" s="5" t="inlineStr"/>
       <c r="J593" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="K593" s="5" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST TİCARET. BIST HİZMETLER. BIST İSTANBUL. BIST ANA. BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100. BIST SINAI. BIST TÜM. BIST TAŞ TOPRAK. BIST HALKA ARZ. BIST ANA. BIST MANİSA</t>
         </is>
       </c>
       <c r="L593" s="5" t="inlineStr"/>
@@ -26884,24 +26940,24 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B594" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>60,50</t>
         </is>
       </c>
       <c r="C594" s="3" t="n">
-        <v>-0.0017</v>
+        <v>-0.0194</v>
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
-          <t>10,00M</t>
+          <t>3,13M</t>
         </is>
       </c>
       <c r="E594" s="4" t="n">
-        <v>48.59</v>
+        <v>47.59</v>
       </c>
       <c r="F594" s="2" t="inlineStr"/>
       <c r="G594" s="2" t="inlineStr"/>
@@ -26909,33 +26965,37 @@
       <c r="I594" s="2" t="inlineStr"/>
       <c r="J594" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="K594" s="2" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="K594" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100. BIST TÜM. BIST HALKA ARZ. BIST MALİ. BIST ANA. BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="L594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="5" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>AKGRT</t>
         </is>
       </c>
       <c r="B595" s="5" t="inlineStr">
         <is>
-          <t>12,03</t>
+          <t>7,20</t>
         </is>
       </c>
       <c r="C595" s="6" t="n">
-        <v>0.09960000000000001</v>
+        <v>-0.0069</v>
       </c>
       <c r="D595" s="5" t="inlineStr">
         <is>
-          <t>120,51M</t>
+          <t>9,00M</t>
         </is>
       </c>
       <c r="E595" s="7" t="n">
-        <v>83.16</v>
+        <v>38.26</v>
       </c>
       <c r="F595" s="5" t="inlineStr"/>
       <c r="G595" s="5" t="inlineStr"/>
@@ -26948,7 +27008,7 @@
       </c>
       <c r="K595" s="5" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST GAYRİMENKUL YO. BIST HALKA ARZ. BIST MALİ. BIST ANA</t>
+          <t>BIST TUM-100. BIST TÜM. BIST SİGORTA. BIST MALİ. BIST YILDIZ. BIST SÜRDÜRÜLEBİLİRLİK</t>
         </is>
       </c>
       <c r="L595" s="5" t="inlineStr"/>
@@ -26956,24 +27016,24 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B596" s="2" t="inlineStr">
         <is>
-          <t>32,14</t>
+          <t>23,70</t>
         </is>
       </c>
       <c r="C596" s="3" t="n">
-        <v>0.0069</v>
+        <v>0.0505</v>
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>5,09M</t>
+          <t>18,74M</t>
         </is>
       </c>
       <c r="E596" s="4" t="n">
-        <v>50.4</v>
+        <v>55.2</v>
       </c>
       <c r="F596" s="2" t="inlineStr"/>
       <c r="G596" s="2" t="inlineStr"/>
@@ -26981,12 +27041,12 @@
       <c r="I596" s="2" t="inlineStr"/>
       <c r="J596" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik. Su. Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST SINAI. BIST TÜM. BIST KİMYA PETROL PLASTİK. BIST HALKA ARZ. BIST KATILIM TÜM. BIST ANA. BIST TEKİRDAĞ</t>
+          <t>BIST ELEKTRIK. BIST TUM-100. BIST TÜM. BIST HALKA ARZ. BIST HİZMETLER. BIST İSTANBUL. BIST KATILIM TÜM. BIST ANA</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr"/>
@@ -26994,37 +27054,45 @@
     <row r="597">
       <c r="A597" s="5" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B597" s="5" t="inlineStr">
         <is>
-          <t>182,0</t>
+          <t>17,30</t>
         </is>
       </c>
       <c r="C597" s="6" t="n">
-        <v>0.005</v>
+        <v>-0.0035</v>
       </c>
       <c r="D597" s="5" t="inlineStr">
         <is>
-          <t>3,33M</t>
+          <t>11,97M</t>
         </is>
       </c>
       <c r="E597" s="7" t="n">
-        <v>58.57</v>
-      </c>
-      <c r="F597" s="5" t="inlineStr"/>
+        <v>46.05</v>
+      </c>
+      <c r="F597" s="6" t="n">
+        <v>1.6352</v>
+      </c>
       <c r="G597" s="5" t="inlineStr"/>
-      <c r="H597" s="5" t="inlineStr"/>
-      <c r="I597" s="5" t="inlineStr"/>
+      <c r="H597" s="6" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="I597" s="5" t="inlineStr">
+        <is>
+          <t>-1.031.71</t>
+        </is>
+      </c>
       <c r="J597" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="K597" s="5" t="inlineStr">
         <is>
-          <t>BIST 100. BIST 100 AĞIRLIK SINIRLAMALI 10. BIST TÜM. BIST İNŞAAT. BIST HALKA ARZ. BIST HİZMETLER. BIST 100-30. BIST KATILIM 100. BIST KATILIM TÜM. BIST 100 AĞIRLIK SINIRLAMALI 25. BIST YILDIZ. BIST KATILIM 50. BIST KATILIM 30. BIST ANKARA. BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100. BIST TÜM. BIST HOLDING VE YATIRIM. BIST MALİ. BIST KATILIM 100. BIST KATILIM TÜM. BIST YILDIZ. BIST KATILIM 50. BIST KONYA</t>
         </is>
       </c>
       <c r="L597" s="5" t="inlineStr"/>
@@ -27032,39 +27100,37 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B598" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>15,82</t>
         </is>
       </c>
       <c r="C598" s="3" t="n">
-        <v>0.0152</v>
+        <v>-0.0561</v>
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
-          <t>95,55M</t>
+          <t>92,49M</t>
         </is>
       </c>
       <c r="E598" s="4" t="n">
-        <v>41.64</v>
+        <v>55.41</v>
       </c>
       <c r="F598" s="2" t="inlineStr"/>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
-      <c r="I598" s="3" t="n">
-        <v>-1.9617</v>
-      </c>
+      <c r="I598" s="2" t="inlineStr"/>
       <c r="J598" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>BIST 100. BIST 100 AĞIRLIK SINIRLAMALI 10. BIST TÜM. BIST SPOR. BIST HİZMETLER. BIST İSTANBUL. BIST 100-30. BIST 100 AĞIRLIK SINIRLAMALI 25. BIST YILDIZ</t>
+          <t>BIST TUM-100. BIST TÜM. BIST GAYRİMENKUL YO. BIST HALKA ARZ. BIST MALİ. BIST KATILIM TÜM. BIST ANA</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr"/>
@@ -27072,41 +27138,39 @@
     <row r="599">
       <c r="A599" s="5" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B599" s="5" t="inlineStr">
         <is>
-          <t>123,1</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="C599" s="6" t="n">
-        <v>0.0008</v>
+        <v>-0.09939999999999999</v>
       </c>
       <c r="D599" s="5" t="inlineStr">
         <is>
-          <t>356,41B</t>
+          <t>98,26M</t>
         </is>
       </c>
       <c r="E599" s="7" t="n">
-        <v>48.58</v>
+        <v>17.32</v>
       </c>
       <c r="F599" s="5" t="inlineStr"/>
       <c r="G599" s="5" t="inlineStr"/>
       <c r="H599" s="6" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="I599" s="6" t="n">
-        <v>-1.2646</v>
-      </c>
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="I599" s="5" t="inlineStr"/>
       <c r="J599" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="K599" s="5" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST TİCARET. BIST HİZMETLER. BIST ANA</t>
+          <t>BIST 100. BIST 100 AĞIRLIK SINIRLAMALI 10. BIST GIDA ICECEK. BIST SINAI. BIST TÜM. BIST HALKA ARZ. BIST 100-30. BIST KATILIM 100. BIST KATILIM TÜM. BIST 100 AĞIRLIK SINIRLAMALI 25. BIST YILDIZ. BIST KATILIM 50</t>
         </is>
       </c>
       <c r="L599" s="5" t="inlineStr"/>
@@ -27114,24 +27178,24 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B600" s="2" t="inlineStr">
         <is>
-          <t>27,12</t>
+          <t>182,0</t>
         </is>
       </c>
       <c r="C600" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.005</v>
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>17,10M</t>
+          <t>3,33M</t>
         </is>
       </c>
       <c r="E600" s="4" t="n">
-        <v>52.08</v>
+        <v>58.57</v>
       </c>
       <c r="F600" s="2" t="inlineStr"/>
       <c r="G600" s="2" t="inlineStr"/>
@@ -27144,7 +27208,7 @@
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST İNŞAAT. BIST HALKA ARZ. BIST HİZMETLER. BIST İSTANBUL. BIST KATILIM TÜM. BIST ANA</t>
+          <t>BIST 100. BIST 100 AĞIRLIK SINIRLAMALI 10. BIST TÜM. BIST İNŞAAT. BIST HALKA ARZ. BIST HİZMETLER. BIST 100-30. BIST KATILIM 100. BIST KATILIM TÜM. BIST 100 AĞIRLIK SINIRLAMALI 25. BIST YILDIZ. BIST KATILIM 50. BIST KATILIM 30. BIST ANKARA. BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr"/>
@@ -27152,24 +27216,24 @@
     <row r="601">
       <c r="A601" s="5" t="inlineStr">
         <is>
-          <t>AKGRT</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B601" s="5" t="inlineStr">
         <is>
-          <t>7,20</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="C601" s="6" t="n">
-        <v>-0.0069</v>
+        <v>0.0323</v>
       </c>
       <c r="D601" s="5" t="inlineStr">
         <is>
-          <t>9,00M</t>
+          <t>186,38M</t>
         </is>
       </c>
       <c r="E601" s="7" t="n">
-        <v>38.26</v>
+        <v>56.01</v>
       </c>
       <c r="F601" s="5" t="inlineStr"/>
       <c r="G601" s="5" t="inlineStr"/>
@@ -27182,7 +27246,7 @@
       </c>
       <c r="K601" s="5" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST SİGORTA. BIST MALİ. BIST YILDIZ. BIST SÜRDÜRÜLEBİLİRLİK</t>
+          <t>BIST TUM-100. BIST SINAI. BIST TÜM. BIST KİMYA PETROL PLASTİK. BIST ANA. BIST KOCAELI</t>
         </is>
       </c>
       <c r="L601" s="5" t="inlineStr"/>
@@ -27190,39 +27254,37 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B602" s="2" t="inlineStr">
         <is>
-          <t>60,05</t>
+          <t>32,14</t>
         </is>
       </c>
       <c r="C602" s="3" t="n">
-        <v>-0.0315</v>
+        <v>0.0069</v>
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>741,64B</t>
+          <t>5,09M</t>
         </is>
       </c>
       <c r="E602" s="4" t="n">
-        <v>55.16</v>
+        <v>50.4</v>
       </c>
       <c r="F602" s="2" t="inlineStr"/>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="3" t="n">
-        <v>-0.2474</v>
-      </c>
+      <c r="I602" s="2" t="inlineStr"/>
       <c r="J602" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST TEKNOLOJİ. BIST BILISIM. BIST İSTANBUL. BIST KATILIM 100. BIST KATILIM TÜM. BIST ANA. BIST TEKNOLOJI AĞIRLIK SINIRLAMALI. BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100. BIST SINAI. BIST TÜM. BIST KİMYA PETROL PLASTİK. BIST HALKA ARZ. BIST KATILIM TÜM. BIST ANA. BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr"/>
@@ -27230,37 +27292,43 @@
     <row r="603">
       <c r="A603" s="5" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B603" s="5" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="C603" s="6" t="n">
-        <v>0.0323</v>
+        <v>0.0803</v>
       </c>
       <c r="D603" s="5" t="inlineStr">
         <is>
-          <t>186,38M</t>
+          <t>38,53M</t>
         </is>
       </c>
       <c r="E603" s="7" t="n">
-        <v>56.01</v>
+        <v>61.31</v>
       </c>
       <c r="F603" s="5" t="inlineStr"/>
       <c r="G603" s="5" t="inlineStr"/>
-      <c r="H603" s="5" t="inlineStr"/>
-      <c r="I603" s="5" t="inlineStr"/>
+      <c r="H603" s="5" t="inlineStr">
+        <is>
+          <t>-19.163.42</t>
+        </is>
+      </c>
+      <c r="I603" s="6" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="J603" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="K603" s="5" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST SINAI. BIST TÜM. BIST KİMYA PETROL PLASTİK. BIST ANA. BIST KOCAELI</t>
+          <t>BIST TUM-100. BIST TÜM. BIST TİCARET. BIST HİZMETLER. BIST İSTANBUL. BIST ANA. BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="L603" s="5" t="inlineStr"/>
@@ -27268,79 +27336,73 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B604" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>244,0</t>
         </is>
       </c>
       <c r="C604" s="3" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0243</v>
       </c>
       <c r="D604" s="2" t="inlineStr">
         <is>
-          <t>15,36M</t>
+          <t>8,92B</t>
         </is>
       </c>
       <c r="E604" s="4" t="n">
-        <v>60.82</v>
+        <v>37.83</v>
       </c>
       <c r="F604" s="2" t="inlineStr"/>
       <c r="G604" s="2" t="inlineStr"/>
-      <c r="H604" s="3" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="I604" s="3" t="n">
-        <v>-1.4124</v>
-      </c>
+      <c r="H604" s="2" t="inlineStr"/>
+      <c r="I604" s="2" t="inlineStr"/>
       <c r="J604" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="K604" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100. BIST TÜM. BIST HİZMETLER. BIST İSTANBUL. BIST YILDIZ</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="K604" s="2" t="inlineStr"/>
       <c r="L604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="5" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B605" s="5" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>60,05</t>
         </is>
       </c>
       <c r="C605" s="6" t="n">
-        <v>-0.0551</v>
+        <v>-0.0315</v>
       </c>
       <c r="D605" s="5" t="inlineStr">
         <is>
-          <t>44,45M</t>
+          <t>741,64B</t>
         </is>
       </c>
       <c r="E605" s="7" t="n">
-        <v>64.51000000000001</v>
+        <v>55.16</v>
       </c>
       <c r="F605" s="5" t="inlineStr"/>
       <c r="G605" s="5" t="inlineStr"/>
       <c r="H605" s="5" t="inlineStr"/>
-      <c r="I605" s="5" t="inlineStr"/>
+      <c r="I605" s="6" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="J605" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="K605" s="5" t="inlineStr">
         <is>
-          <t>BIST TUM-100. BIST TÜM. BIST HOLDING VE YATIRIM. BIST MALİ. BIST ANA</t>
+          <t>BIST TUM-100. BIST TÜM. BIST TEKNOLOJİ. BIST BILISIM. BIST İSTANBUL. BIST KATILIM 100. BIST KATILIM TÜM. BIST ANA. BIST TEKNOLOJI AĞIRLIK SINIRLAMALI. BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="L605" s="5" t="inlineStr"/>
@@ -27367,7 +27429,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>02.04.2026 16:17</t>
+          <t>02.04.2026 16:24</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-02.xlsx
+++ b/data/bist_screener_2026-04-02.xlsx
@@ -25615,23 +25615,23 @@
     <row r="579">
       <c r="A579" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B579" s="7" t="n">
-        <v>3.43</v>
+        <v>244</v>
       </c>
       <c r="C579" s="8" t="n">
-        <v>-0.0551</v>
+        <v>0.0243</v>
       </c>
       <c r="D579" s="9" t="n">
-        <v>44450000</v>
+        <v>8920</v>
       </c>
       <c r="E579" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.2578</v>
       </c>
       <c r="F579" s="7" t="n">
-        <v>64.51000000000001</v>
+        <v>37.83</v>
       </c>
       <c r="G579" s="6" t="inlineStr"/>
       <c r="H579" s="6" t="inlineStr"/>
@@ -25639,53 +25639,45 @@
       <c r="J579" s="6" t="inlineStr"/>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L579" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L579" s="6" t="inlineStr"/>
       <c r="M579" s="6" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>AKGRT</t>
         </is>
       </c>
       <c r="B580" s="3" t="n">
-        <v>123.1</v>
+        <v>7.2</v>
       </c>
       <c r="C580" s="4" t="n">
-        <v>0.0008</v>
+        <v>-0.0069</v>
       </c>
       <c r="D580" s="5" t="n">
-        <v>356410</v>
+        <v>9000000</v>
       </c>
       <c r="E580" s="4" t="n">
-        <v>0.1071</v>
+        <v>0.28</v>
       </c>
       <c r="F580" s="3" t="n">
-        <v>48.58</v>
+        <v>38.26</v>
       </c>
       <c r="G580" s="2" t="inlineStr"/>
       <c r="H580" s="2" t="inlineStr"/>
-      <c r="I580" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J580" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I580" s="2" t="inlineStr"/>
+      <c r="J580" s="2" t="inlineStr"/>
       <c r="K580" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L580" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST SİGORTA, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK</t>
         </is>
       </c>
       <c r="M580" s="2" t="inlineStr"/>
@@ -25693,23 +25685,23 @@
     <row r="581">
       <c r="A581" s="6" t="inlineStr">
         <is>
-          <t>AKGRT</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B581" s="7" t="n">
-        <v>7.2</v>
+        <v>27.12</v>
       </c>
       <c r="C581" s="8" t="n">
-        <v>-0.0069</v>
+        <v>0.0015</v>
       </c>
       <c r="D581" s="9" t="n">
-        <v>9000000</v>
+        <v>17100000</v>
       </c>
       <c r="E581" s="8" t="n">
-        <v>0.28</v>
+        <v>0.2667</v>
       </c>
       <c r="F581" s="7" t="n">
-        <v>38.26</v>
+        <v>52.08</v>
       </c>
       <c r="G581" s="6" t="inlineStr"/>
       <c r="H581" s="6" t="inlineStr"/>
@@ -25717,12 +25709,12 @@
       <c r="J581" s="6" t="inlineStr"/>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST SİGORTA, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M581" s="6" t="inlineStr"/>
@@ -25730,23 +25722,21 @@
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B582" s="3" t="n">
-        <v>27.12</v>
+        <v>15.82</v>
       </c>
       <c r="C582" s="4" t="n">
-        <v>0.0015</v>
+        <v>-0.0561</v>
       </c>
       <c r="D582" s="5" t="n">
-        <v>17100000</v>
-      </c>
-      <c r="E582" s="4" t="n">
-        <v>0.2667</v>
-      </c>
+        <v>92490000</v>
+      </c>
+      <c r="E582" s="2" t="inlineStr"/>
       <c r="F582" s="3" t="n">
-        <v>52.08</v>
+        <v>55.41</v>
       </c>
       <c r="G582" s="2" t="inlineStr"/>
       <c r="H582" s="2" t="inlineStr"/>
@@ -25754,12 +25744,12 @@
       <c r="J582" s="2" t="inlineStr"/>
       <c r="K582" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L582" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M582" s="2" t="inlineStr"/>
@@ -25767,38 +25757,40 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0.0152</v>
+        <v>0.0803</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>95550000</v>
+        <v>38530000</v>
       </c>
       <c r="E583" s="8" t="n">
-        <v>0.6898000000000001</v>
+        <v>0.7119</v>
       </c>
       <c r="F583" s="7" t="n">
-        <v>41.64</v>
+        <v>61.31</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="6" t="inlineStr"/>
+      <c r="I583" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
       <c r="J583" s="8" t="n">
-        <v>-2.0083</v>
+        <v>-0.8093</v>
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M583" s="6" t="inlineStr"/>
@@ -25806,34 +25798,38 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>32.14</v>
+        <v>8.15</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>0.0069</v>
+        <v>-0.09939999999999999</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>5090000</v>
-      </c>
-      <c r="E584" s="2" t="inlineStr"/>
+        <v>98260000</v>
+      </c>
+      <c r="E584" s="4" t="n">
+        <v>0.2478</v>
+      </c>
       <c r="F584" s="3" t="n">
-        <v>50.4</v>
+        <v>17.32</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
-      <c r="I584" s="2" t="inlineStr"/>
+      <c r="I584" s="4" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
       <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25841,21 +25837,21 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>13.36</v>
+        <v>60.5</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>-0.0052</v>
+        <v>-0.0194</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>71200000</v>
+        <v>3130000</v>
       </c>
       <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>54.58</v>
+        <v>47.59</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25863,12 +25859,12 @@
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25876,21 +25872,21 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>60.5</v>
+        <v>35.82</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0194</v>
+        <v>-0.017</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>3130000</v>
+        <v>4910000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>47.59</v>
+        <v>46.44</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25898,12 +25894,12 @@
       <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25911,38 +25907,34 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>8.15</v>
+        <v>27.1</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.09939999999999999</v>
+        <v>-0.0266</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>98260000</v>
-      </c>
-      <c r="E587" s="8" t="n">
-        <v>0.2478</v>
-      </c>
+        <v>21120000</v>
+      </c>
+      <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>17.32</v>
+        <v>54.93</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="8" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
+      <c r="I587" s="6" t="inlineStr"/>
       <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25950,38 +25942,42 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>60.05</v>
+        <v>17.3</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0315</v>
+        <v>-0.0035</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>741640</v>
+        <v>11970000</v>
       </c>
       <c r="E588" s="4" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.9246</v>
       </c>
       <c r="F588" s="3" t="n">
-        <v>55.16</v>
-      </c>
-      <c r="G588" s="2" t="inlineStr"/>
+        <v>46.05</v>
+      </c>
+      <c r="G588" s="3" t="n">
+        <v>163.52</v>
+      </c>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="2" t="inlineStr"/>
+      <c r="I588" s="4" t="n">
+        <v>0.0028</v>
+      </c>
       <c r="J588" s="4" t="n">
-        <v>0.4139</v>
+        <v>-10.3171</v>
       </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -25989,40 +25985,34 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>2.96</v>
+        <v>44.58</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0803</v>
+        <v>0.0059</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>38530000</v>
-      </c>
-      <c r="E589" s="8" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>30630000</v>
+      </c>
+      <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>61.31</v>
+        <v>62.46</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J589" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I589" s="6" t="inlineStr"/>
+      <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26030,23 +26020,21 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>244</v>
+        <v>23.7</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>0.0243</v>
+        <v>0.0505</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>8920</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>18740000</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>37.83</v>
+        <v>55.2</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
@@ -26054,179 +26042,199 @@
       <c r="J590" s="2" t="inlineStr"/>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L590" s="2" t="inlineStr"/>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
+      <c r="L590" s="2" t="inlineStr">
+        <is>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>82.76000000000001</v>
+        <v>32.14</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.0059</v>
+        <v>0.0069</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>18830000</v>
+        <v>5090000</v>
       </c>
       <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>43.97</v>
+        <v>50.4</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
       <c r="I591" s="6" t="inlineStr"/>
       <c r="J591" s="6" t="inlineStr"/>
-      <c r="K591" s="6" t="inlineStr"/>
-      <c r="L591" s="6" t="inlineStr"/>
+      <c r="K591" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+        </is>
+      </c>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>91.5</v>
+        <v>13.36</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>-0.006</v>
+        <v>-0.0052</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>25120</v>
-      </c>
-      <c r="E592" s="4" t="n">
-        <v>0.58</v>
-      </c>
+        <v>71200000</v>
+      </c>
+      <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>45.83</v>
+        <v>54.58</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J592" s="4" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L592" s="2" t="inlineStr"/>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L592" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>27.1</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.0266</v>
+        <v>-0.0469</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>21120000</v>
-      </c>
-      <c r="E593" s="6" t="inlineStr"/>
+        <v>199280</v>
+      </c>
+      <c r="E593" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F593" s="7" t="n">
-        <v>54.93</v>
+        <v>45.93</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
-      <c r="I593" s="6" t="inlineStr"/>
-      <c r="J593" s="6" t="inlineStr"/>
+      <c r="I593" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J593" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L593" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L593" s="6" t="inlineStr"/>
       <c r="M593" s="6" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.0469</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>199280</v>
+        <v>15360000</v>
       </c>
       <c r="E594" s="4" t="n">
-        <v>0.95</v>
+        <v>0.1672</v>
       </c>
       <c r="F594" s="3" t="n">
-        <v>45.93</v>
+        <v>60.82</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
       <c r="I594" s="4" t="n">
-        <v>-23.6291</v>
+        <v>-5.3262</v>
       </c>
       <c r="J594" s="4" t="n">
-        <v>-0.4678</v>
+        <v>-4.2562</v>
       </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L594" s="2" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L594" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>2.56</v>
+        <v>60.05</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0323</v>
+        <v>-0.0315</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>186380000</v>
-      </c>
-      <c r="E595" s="6" t="inlineStr"/>
+        <v>741640</v>
+      </c>
+      <c r="E595" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F595" s="7" t="n">
-        <v>56.01</v>
+        <v>55.16</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
       <c r="I595" s="6" t="inlineStr"/>
-      <c r="J595" s="6" t="inlineStr"/>
+      <c r="J595" s="8" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26234,21 +26242,23 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>12.03</v>
+        <v>3.43</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>-0.0551</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>120510000</v>
-      </c>
-      <c r="E596" s="2" t="inlineStr"/>
+        <v>44450000</v>
+      </c>
+      <c r="E596" s="4" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F596" s="3" t="n">
-        <v>83.16</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
@@ -26261,7 +26271,7 @@
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26269,21 +26279,21 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>35.82</v>
+        <v>12.03</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.017</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>4910000</v>
+        <v>120510000</v>
       </c>
       <c r="E597" s="6" t="inlineStr"/>
       <c r="F597" s="7" t="n">
-        <v>46.44</v>
+        <v>83.16</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
@@ -26291,12 +26301,12 @@
       <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26304,52 +26314,60 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>5.74</v>
+        <v>2.68</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0017</v>
+        <v>0.0152</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="E598" s="2" t="inlineStr"/>
+        <v>95550000</v>
+      </c>
+      <c r="E598" s="4" t="n">
+        <v>0.6898000000000001</v>
+      </c>
       <c r="F598" s="3" t="n">
-        <v>48.59</v>
+        <v>41.64</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
       <c r="I598" s="2" t="inlineStr"/>
-      <c r="J598" s="2" t="inlineStr"/>
+      <c r="J598" s="4" t="n">
+        <v>-2.0083</v>
+      </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr"/>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>44.58</v>
+        <v>2.56</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0059</v>
+        <v>0.0323</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>30630000</v>
+        <v>186380000</v>
       </c>
       <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>62.46</v>
+        <v>56.01</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
@@ -26357,12 +26375,12 @@
       <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26370,21 +26388,21 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>15.82</v>
+        <v>5.74</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.0561</v>
+        <v>-0.0017</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>92490000</v>
+        <v>10000000</v>
       </c>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>55.41</v>
+        <v>48.59</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
@@ -26395,50 +26413,46 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L600" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+      <c r="L600" s="2" t="inlineStr"/>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>3.12</v>
+        <v>123.1</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>15360000</v>
+        <v>356410</v>
       </c>
       <c r="E601" s="8" t="n">
-        <v>0.1672</v>
+        <v>0.1071</v>
       </c>
       <c r="F601" s="7" t="n">
-        <v>60.82</v>
+        <v>48.58</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="8" t="n">
-        <v>-5.3262</v>
+        <v>-3.6635</v>
       </c>
       <c r="J601" s="8" t="n">
-        <v>-4.2562</v>
+        <v>-0.4897</v>
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26446,56 +26460,58 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>182</v>
+        <v>91.5</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.005</v>
+        <v>-0.006</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>3330000</v>
-      </c>
-      <c r="E602" s="2" t="inlineStr"/>
+        <v>25120</v>
+      </c>
+      <c r="E602" s="4" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F602" s="3" t="n">
-        <v>58.57</v>
+        <v>45.83</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="2" t="inlineStr"/>
-      <c r="J602" s="2" t="inlineStr"/>
+      <c r="I602" s="4" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J602" s="4" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L602" s="2" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L602" s="2" t="inlineStr"/>
       <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>149.6</v>
+        <v>182</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.1</v>
+        <v>0.005</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>15490000</v>
+        <v>3330000</v>
       </c>
       <c r="E603" s="6" t="inlineStr"/>
       <c r="F603" s="7" t="n">
-        <v>74.16</v>
+        <v>58.57</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
@@ -26503,12 +26519,12 @@
       <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26516,77 +26532,61 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>23.7</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0505</v>
+        <v>-0.0059</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>18740000</v>
+        <v>18830000</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>55.2</v>
+        <v>43.97</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
       <c r="I604" s="2" t="inlineStr"/>
       <c r="J604" s="2" t="inlineStr"/>
-      <c r="K604" s="2" t="inlineStr">
-        <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr">
-        <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+      <c r="K604" s="2" t="inlineStr"/>
+      <c r="L604" s="2" t="inlineStr"/>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>17.3</v>
+        <v>149.6</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.0035</v>
+        <v>0.1</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>11970000</v>
-      </c>
-      <c r="E605" s="8" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>15490000</v>
+      </c>
+      <c r="E605" s="6" t="inlineStr"/>
       <c r="F605" s="7" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="G605" s="7" t="n">
-        <v>163.52</v>
-      </c>
+        <v>74.16</v>
+      </c>
+      <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="8" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J605" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I605" s="6" t="inlineStr"/>
+      <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26613,7 +26613,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>02.04.2026 19:19</t>
+          <t>02.04.2026 19:46</t>
         </is>
       </c>
     </row>
